--- a/setlists/Stove Up.xlsx
+++ b/setlists/Stove Up.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="229">
   <si>
     <t xml:space="preserve">4.11.26
 O'Donoghue's Brunswick</t>
@@ -639,7 +639,25 @@
     <t xml:space="preserve">Set 3</t>
   </si>
   <si>
-    <t xml:space="preserve">Nothin’ But A Good</t>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Nothin’ But A Good</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ↓</t>
+    </r>
   </si>
   <si>
     <r>
@@ -675,6 +693,27 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Would?</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve"> - I Was Made 4</t>
   </si>
   <si>
@@ -757,7 +796,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -834,6 +873,12 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -935,7 +980,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1048,6 +1093,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1056,11 +1105,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2247,12 +2296,8 @@
       </c>
     </row>
     <row r="59" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0"/>
-      <c r="B59" s="0"/>
-      <c r="C59" s="0"/>
-      <c r="D59" s="0"/>
-      <c r="E59" s="0"/>
-      <c r="F59" s="0"/>
+      <c r="A59" s="2"/>
+      <c r="F59" s="2"/>
     </row>
     <row r="60" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="22"/>
@@ -2620,16 +2665,16 @@
       <c r="A3" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="B3" s="27" t="s">
-        <v>59</v>
-      </c>
-      <c r="C3" s="28" t="s">
+      <c r="B3" s="28" t="s">
         <v>203</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="26" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B4" s="27" t="s">
         <v>62</v>
@@ -2640,21 +2685,21 @@
     </row>
     <row r="5" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="26" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C5" s="26" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="29" t="s">
         <v>21</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C6" s="26" t="s">
         <v>119</v>
@@ -2662,10 +2707,10 @@
     </row>
     <row r="7" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="26" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C7" s="26" t="s">
         <v>122</v>
@@ -2673,20 +2718,20 @@
     </row>
     <row r="8" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="26" t="s">
-        <v>210</v>
-      </c>
-      <c r="B8" s="29" t="s">
+        <v>211</v>
+      </c>
+      <c r="B8" s="30" t="s">
         <v>76</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="B9" s="29" t="s">
+        <v>213</v>
+      </c>
+      <c r="B9" s="30" t="s">
         <v>79</v>
       </c>
       <c r="C9" s="26" t="s">
@@ -2695,9 +2740,9 @@
     </row>
     <row r="10" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="26" t="s">
-        <v>213</v>
-      </c>
-      <c r="B10" s="29" t="s">
+        <v>214</v>
+      </c>
+      <c r="B10" s="30" t="s">
         <v>81</v>
       </c>
       <c r="C10" s="26" t="s">
@@ -2708,30 +2753,30 @@
       <c r="A11" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="29" t="s">
         <v>84</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="26" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="26" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C13" s="26" t="s">
         <v>137</v>
@@ -2745,18 +2790,18 @@
         <v>93</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="26" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2764,19 +2809,19 @@
         <v>50</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="30"/>
+      <c r="A17" s="31"/>
       <c r="B17" s="26" t="s">
-        <v>226</v>
-      </c>
-      <c r="C17" s="31" t="s">
         <v>227</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/setlists/Stove Up.xlsx
+++ b/setlists/Stove Up.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="1" state="visible" r:id="rId3"/>
@@ -21,11 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="229">
-  <si>
-    <t xml:space="preserve">4.11.26
-O'Donoghue's Brunswick</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="220">
   <si>
     <t xml:space="preserve">SET 1</t>
   </si>
@@ -188,9 +184,6 @@
     <t xml:space="preserve">Romantics</t>
   </si>
   <si>
-    <t xml:space="preserve">15 songs</t>
-  </si>
-  <si>
     <t xml:space="preserve">SET 2</t>
   </si>
   <si>
@@ -349,9 +342,6 @@
     <t xml:space="preserve">Simple Minds</t>
   </si>
   <si>
-    <t xml:space="preserve">16 songs</t>
-  </si>
-  <si>
     <t xml:space="preserve">SET 3</t>
   </si>
   <si>
@@ -420,85 +410,124 @@
     <t xml:space="preserve">Seven Mary Three</t>
   </si>
   <si>
+    <t xml:space="preserve">Movin' Out ↓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dm – ends on D Major</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billy Joel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">American Band ↓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grand Funk Railroad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hey Jealousy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">December ↓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K+I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G F C Bb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santa Monica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Everclear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mary Jane's Last Dance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V: Am G D Am  C: D A  G, Harp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Petty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Champagne Supernova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oasis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D C E G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cracker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Come Together</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V: Dm A G  C: Bm G A Dm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beatles</t>
+  </si>
+  <si>
     <t xml:space="preserve">Beast of Burden</t>
   </si>
   <si>
     <t xml:space="preserve">E B C#m A – A E/G# A B</t>
   </si>
   <si>
-    <t xml:space="preserve">Movin' Out ↓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dm – ends on D Major</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billy Joel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">American Band ↓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grand Funk Railroad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hey Jealousy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">December ↓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K+I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G F C Bb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santa Monica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Everclear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mary Jane's Last Dance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V: Am G D Am  C: D A  G, Harp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Petty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Champagne Supernova</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oasis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D C E G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cracker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Come Together</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V: Dm A G  C: Bm G A Dm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beatles</t>
+    <t xml:space="preserve">Love Song</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V: Am9 G F G C: F G Am C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Cure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Misc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Born to Be Wild</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steppenwolf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">China Grove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doobie Brothers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cinnamon Girl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E (in standard for harp)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U2</t>
   </si>
   <si>
     <t xml:space="preserve">Good</t>
@@ -510,126 +539,69 @@
     <t xml:space="preserve">Better Than Ezra</t>
   </si>
   <si>
-    <t xml:space="preserve">Love Song</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V: Am9 G F G C: F G Am C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Cure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Misc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baby Hold On</t>
+    <t xml:space="preserve">Green River</t>
   </si>
   <si>
     <t xml:space="preserve">??</t>
   </si>
   <si>
+    <t xml:space="preserve">E7 C A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hold the Line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning To Fly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F C Am G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Let's Go</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Cars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paranoid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black Sabbath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Possum Kingdom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toadies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run To You</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She's A Beauty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Tubes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shimmer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two Tickets To Paradise</t>
+  </si>
+  <si>
     <t xml:space="preserve">Eddie Money</t>
   </si>
   <si>
-    <t xml:space="preserve">Born to Be Wild</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Steppenwolf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">China Grove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doobie Brothers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cinnamon Girl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fight for your Right to Party</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beastie Boys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Green River</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E7 C A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hold the Line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning To Fly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F C Am G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Knocking On Heaven’s Door</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G&amp;R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Let's Go</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Cars</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paranoid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Black Sabbath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Possum Kingdom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toadies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Run To You</t>
-  </si>
-  <si>
-    <t xml:space="preserve">She's A Beauty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Tubes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shimmer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Those Shoes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eagles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trick of the Light</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Who</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two Tickets To Paradise</t>
-  </si>
-  <si>
     <t xml:space="preserve">Set 1</t>
   </si>
   <si>
@@ -639,25 +611,7 @@
     <t xml:space="preserve">Set 3</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Nothin’ But A Good</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> ↓</t>
-    </r>
+    <t xml:space="preserve">Nothin’ But A Good ↓</t>
   </si>
   <si>
     <r>
@@ -693,25 +647,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Would?</t>
-    </r>
+    <t xml:space="preserve"> - Would?</t>
   </si>
   <si>
     <t xml:space="preserve"> - I Was Made 4</t>
@@ -750,15 +686,15 @@
     <t xml:space="preserve"> - American Band ↓</t>
   </si>
   <si>
+    <t xml:space="preserve"> - Hey Jealousy</t>
+  </si>
+  <si>
     <t xml:space="preserve"> - Long Way Down ↓</t>
   </si>
   <si>
     <t xml:space="preserve">Working For Week ↓</t>
   </si>
   <si>
-    <t xml:space="preserve"> - Hey Jealousy</t>
-  </si>
-  <si>
     <t xml:space="preserve"> - Counting Blue Cars</t>
   </si>
   <si>
@@ -768,25 +704,25 @@
     <t xml:space="preserve"> - Santa Monica</t>
   </si>
   <si>
+    <t xml:space="preserve">Mary Jane's Last</t>
+  </si>
+  <si>
     <t xml:space="preserve"> - Bad Case of Loving</t>
   </si>
   <si>
     <t xml:space="preserve"> - Flagpole Sitta</t>
   </si>
   <si>
-    <t xml:space="preserve">Mary Jane's Last</t>
+    <t xml:space="preserve">Champ Supernova</t>
   </si>
   <si>
     <t xml:space="preserve">My Own Worst En ↓</t>
   </si>
   <si>
-    <t xml:space="preserve">Champ Supernova</t>
-  </si>
-  <si>
     <t xml:space="preserve"> - Don't You Forget</t>
   </si>
   <si>
-    <t xml:space="preserve">+ Low, Come Together, Good, Lovesong</t>
+    <t xml:space="preserve">Beast_o_B, Low, Come Together, Lovesong</t>
   </si>
 </sst>
 </file>
@@ -819,12 +755,7 @@
       <family val="0"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
+      <b val="true"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -832,7 +763,12 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -875,12 +811,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b val="true"/>
       <sz val="16"/>
       <color theme="1"/>
@@ -890,11 +820,18 @@
     </font>
     <font>
       <sz val="16"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
+      <i val="true"/>
       <sz val="12"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -1001,15 +938,31 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1017,35 +970,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1053,23 +990,23 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1093,16 +1030,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -1312,1305 +1249,1238 @@
       <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="6"/>
+      <c r="C1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="7"/>
       <c r="B2" s="8" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="D2" s="8" t="n">
+        <v>78</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4"/>
-      <c r="B3" s="5" t="s">
+      <c r="A3" s="10"/>
+      <c r="B3" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="5" t="n">
-        <v>78</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>9</v>
+      <c r="D3" s="8" t="n">
+        <v>124</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="10"/>
-      <c r="B4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>124</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="6" t="s">
+      <c r="B4" s="8" t="s">
         <v>12</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>120</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10"/>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>77</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="11"/>
+      <c r="B6" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>120</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10"/>
-      <c r="B6" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>77</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>20</v>
+      <c r="D6" s="8" t="n">
+        <v>91</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="11"/>
-      <c r="B7" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>91</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="6" t="s">
+      <c r="B7" s="8" t="s">
         <v>23</v>
       </c>
+      <c r="C7" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>112</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="11"/>
-      <c r="B8" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>112</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="6" t="s">
+      <c r="A8" s="13"/>
+      <c r="B8" s="8" t="s">
         <v>26</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>135</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="13"/>
-      <c r="B9" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>135</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="6" t="s">
+      <c r="B9" s="8" t="s">
         <v>29</v>
       </c>
+      <c r="C9" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>138</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13"/>
-      <c r="B10" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>138</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" s="6" t="s">
+      <c r="A10" s="10"/>
+      <c r="B10" s="8" t="s">
         <v>32</v>
       </c>
+      <c r="C10" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>142</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10"/>
-      <c r="B11" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>142</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F11" s="6" t="s">
+      <c r="A11" s="11"/>
+      <c r="B11" s="8" t="s">
         <v>35</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>121</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11"/>
-      <c r="B12" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>121</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F12" s="6" t="s">
+      <c r="B12" s="8" t="s">
         <v>38</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>168</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11"/>
-      <c r="B13" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>168</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F13" s="6" t="s">
+      <c r="B13" s="8" t="s">
         <v>41</v>
       </c>
+      <c r="C13" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="11"/>
-      <c r="B14" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F14" s="6" t="s">
+      <c r="A14" s="10"/>
+      <c r="B14" s="8" t="s">
         <v>44</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>105</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="10"/>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>146</v>
+      </c>
+      <c r="E15" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>105</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>47</v>
+      <c r="F15" s="9" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10"/>
-      <c r="B16" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>146</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F16" s="6" t="s">
+      <c r="A16" s="7"/>
+      <c r="B16" s="8" t="s">
         <v>49</v>
       </c>
+      <c r="C16" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>160</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4"/>
-      <c r="B17" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>160</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F17" s="6" t="s">
+      <c r="A17" s="7"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="14"/>
+    </row>
+    <row r="18" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7"/>
+      <c r="B18" s="5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="14"/>
+    </row>
+    <row r="19" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="14"/>
-    </row>
-    <row r="19" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4"/>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="14"/>
+      <c r="C19" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>129</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="15" t="s">
-        <v>55</v>
-      </c>
+      <c r="A20" s="7"/>
       <c r="B20" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>129</v>
-      </c>
-      <c r="E20" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="C20" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E20" s="8" t="s">
         <v>58</v>
       </c>
+      <c r="F20" s="9" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4"/>
+      <c r="A21" s="10"/>
       <c r="B21" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E21" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="C21" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>177</v>
+      </c>
+      <c r="E21" s="8" t="s">
         <v>61</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="10"/>
       <c r="B22" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>177</v>
-      </c>
-      <c r="E22" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="C22" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="E22" s="8" t="s">
         <v>64</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="10"/>
       <c r="B23" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="E23" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="C23" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>132</v>
+      </c>
+      <c r="E23" s="8" t="s">
         <v>67</v>
       </c>
+      <c r="F23" s="9" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10"/>
+      <c r="A24" s="17"/>
       <c r="B24" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>132</v>
-      </c>
-      <c r="E24" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="C24" s="8" t="s">
         <v>70</v>
       </c>
+      <c r="D24" s="8" t="n">
+        <v>152</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="17"/>
-      <c r="B25" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>152</v>
-      </c>
-      <c r="E25" s="5" t="s">
+      <c r="A25" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="F25" s="6" t="s">
+      <c r="B25" s="18" t="s">
         <v>74</v>
       </c>
+      <c r="C25" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>124</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="s">
-        <v>75</v>
-      </c>
+      <c r="A26" s="7"/>
       <c r="B26" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>124</v>
-      </c>
-      <c r="E26" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="C26" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>142</v>
+      </c>
+      <c r="E26" s="8"/>
+      <c r="F26" s="9" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4"/>
+      <c r="A27" s="7"/>
       <c r="B27" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="C27" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>142</v>
-      </c>
-      <c r="E27" s="5"/>
-      <c r="F27" s="6" t="s">
+      <c r="C27" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E27" s="8"/>
+      <c r="F27" s="9" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4"/>
-      <c r="B28" s="18" t="s">
+      <c r="A28" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="C28" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="E28" s="5"/>
-      <c r="F28" s="6" t="s">
+      <c r="B28" s="12" t="s">
         <v>82</v>
       </c>
+      <c r="C28" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="8" t="n">
+        <v>119</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>119</v>
-      </c>
-      <c r="E29" s="5" t="s">
+      <c r="A29" s="10"/>
+      <c r="B29" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="F29" s="6" t="s">
+      <c r="C29" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>147</v>
+      </c>
+      <c r="E29" s="8" t="s">
         <v>86</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="10"/>
-      <c r="B30" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>147</v>
-      </c>
-      <c r="E30" s="5" t="s">
+      <c r="B30" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="C30" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>102</v>
+      </c>
+      <c r="E30" s="8" t="s">
         <v>89</v>
       </c>
+      <c r="F30" s="9" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="10"/>
-      <c r="B31" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>102</v>
-      </c>
-      <c r="E31" s="5" t="s">
+      <c r="A31" s="11"/>
+      <c r="B31" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="F31" s="6" t="s">
+      <c r="C31" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>139</v>
+      </c>
+      <c r="E31" s="8" t="s">
         <v>92</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="11"/>
-      <c r="B32" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>139</v>
-      </c>
-      <c r="E32" s="5" t="s">
+      <c r="B32" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="F32" s="6" t="s">
+      <c r="C32" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>145</v>
+      </c>
+      <c r="E32" s="8" t="s">
         <v>95</v>
       </c>
+      <c r="F32" s="9" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="11"/>
-      <c r="B33" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>145</v>
-      </c>
-      <c r="E33" s="5" t="s">
+      <c r="A33" s="10"/>
+      <c r="B33" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="F33" s="6" t="s">
+      <c r="C33" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>103</v>
+      </c>
+      <c r="E33" s="8" t="s">
         <v>98</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="10"/>
-      <c r="B34" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D34" s="5" t="n">
+      <c r="B34" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>111</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="19"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="20"/>
+    </row>
+    <row r="36" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="4"/>
+      <c r="B36" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="E34" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="10"/>
-      <c r="B35" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>111</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="F35" s="6" t="s">
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="14"/>
+    </row>
+    <row r="37" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="10"/>
+      <c r="B37" s="8" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="36" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="19" t="s">
+      <c r="C37" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D37" s="8" t="n">
+        <v>110</v>
+      </c>
+      <c r="E37" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="B36" s="19"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="19"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="20"/>
-    </row>
-    <row r="37" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="7"/>
-      <c r="B37" s="8" t="s">
+      <c r="F37" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="14"/>
     </row>
     <row r="38" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="10"/>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C38" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D38" s="5" t="n">
+      <c r="C38" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D38" s="8" t="n">
+        <v>128</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="7"/>
+      <c r="B39" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="E38" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="10"/>
-      <c r="B39" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>128</v>
-      </c>
-      <c r="E39" s="5" t="s">
+      <c r="C39" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>177</v>
+      </c>
+      <c r="E39" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="F39" s="6" t="s">
+      <c r="F39" s="9" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4"/>
-      <c r="B40" s="5" t="s">
+      <c r="A40" s="7"/>
+      <c r="B40" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="C40" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D40" s="5" t="n">
-        <v>177</v>
-      </c>
-      <c r="E40" s="5" t="s">
+      <c r="C40" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>149</v>
+      </c>
+      <c r="E40" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="F40" s="6" t="s">
+      <c r="F40" s="9" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4"/>
-      <c r="B41" s="5" t="s">
+      <c r="A41" s="7"/>
+      <c r="B41" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="C41" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D41" s="5" t="n">
-        <v>149</v>
-      </c>
-      <c r="E41" s="5" t="s">
+      <c r="C41" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>101</v>
+      </c>
+      <c r="E41" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="F41" s="6" t="s">
+      <c r="F41" s="9" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4"/>
-      <c r="B42" s="5" t="s">
+      <c r="A42" s="10"/>
+      <c r="B42" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="C42" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D42" s="5" t="n">
-        <v>101</v>
-      </c>
-      <c r="E42" s="5" t="s">
+      <c r="C42" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>176</v>
+      </c>
+      <c r="E42" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="F42" s="6" t="s">
+      <c r="F42" s="9" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="10"/>
-      <c r="B43" s="5" t="s">
+      <c r="B43" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="C43" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D43" s="5" t="n">
-        <v>176</v>
-      </c>
-      <c r="E43" s="5" t="s">
+      <c r="C43" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>81</v>
+      </c>
+      <c r="E43" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="F43" s="6" t="s">
+      <c r="F43" s="9" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="10"/>
-      <c r="B44" s="5" t="s">
+      <c r="B44" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="C44" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D44" s="5" t="n">
-        <v>81</v>
-      </c>
-      <c r="E44" s="5" t="s">
+      <c r="C44" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>134</v>
+      </c>
+      <c r="E44" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="F44" s="6" t="s">
+      <c r="F44" s="9" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="4"/>
-      <c r="B45" s="5" t="s">
+      <c r="A45" s="10"/>
+      <c r="B45" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="C45" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D45" s="5" t="n">
-        <v>101</v>
-      </c>
-      <c r="E45" s="5" t="s">
+      <c r="C45" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>128</v>
+      </c>
+      <c r="E45" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="F45" s="14" t="s">
-        <v>109</v>
+      <c r="F45" s="9" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="10"/>
-      <c r="B46" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D46" s="5" t="n">
+      <c r="B46" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D46" s="8" t="n">
+        <v>153</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="11"/>
+      <c r="B47" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="D47" s="8" t="n">
+        <v>122</v>
+      </c>
+      <c r="E47" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="E46" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="F46" s="6" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="10"/>
-      <c r="B47" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D47" s="5" t="n">
-        <v>128</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="F47" s="6" t="s">
+      <c r="F47" s="9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="11"/>
+      <c r="B48" s="8" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="48" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="10"/>
-      <c r="B48" s="5" t="s">
+      <c r="C48" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D48" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E48" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="C48" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D48" s="5" t="n">
-        <v>153</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="F48" s="6" t="s">
-        <v>29</v>
+      <c r="F48" s="9" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="11"/>
-      <c r="B49" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C49" s="5" t="s">
+      <c r="A49" s="7"/>
+      <c r="B49" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="D49" s="5" t="n">
-        <v>122</v>
-      </c>
-      <c r="E49" s="5" t="s">
+      <c r="C49" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D49" s="8" t="n">
+        <v>85</v>
+      </c>
+      <c r="E49" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="F49" s="6" t="s">
-        <v>82</v>
+      <c r="F49" s="9" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="11"/>
-      <c r="B50" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D50" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E50" s="5" t="s">
+      <c r="A50" s="7"/>
+      <c r="B50" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="F50" s="6" t="s">
+      <c r="C50" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D50" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F50" s="9" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4"/>
-      <c r="B51" s="5" t="s">
+      <c r="A51" s="0"/>
+      <c r="B51" s="0"/>
+      <c r="C51" s="0"/>
+      <c r="D51" s="0"/>
+      <c r="E51" s="0"/>
+      <c r="F51" s="0"/>
+    </row>
+    <row r="52" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="7"/>
+      <c r="B52" s="21" t="s">
         <v>143</v>
       </c>
-      <c r="C51" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D51" s="5" t="n">
-        <v>85</v>
-      </c>
-      <c r="E51" s="5" t="s">
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="9"/>
+    </row>
+    <row r="53" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="4"/>
+      <c r="B53" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="F51" s="6" t="s">
+      <c r="C53" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D53" s="8" t="n">
+        <v>174</v>
+      </c>
+      <c r="E53" s="8" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="52" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4"/>
-      <c r="B52" s="5" t="s">
+      <c r="F53" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="C52" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D52" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="E52" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F52" s="6" t="s">
+    </row>
+    <row r="54" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="7"/>
+      <c r="B54" s="8" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="53" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B53" s="5"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="5"/>
-      <c r="E53" s="5"/>
-      <c r="F53" s="6"/>
-    </row>
-    <row r="54" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4"/>
-      <c r="B54" s="21" t="s">
+      <c r="C54" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" s="8" t="n">
+        <v>83</v>
+      </c>
+      <c r="E54" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="C54" s="5"/>
-      <c r="D54" s="5"/>
-      <c r="E54" s="5"/>
-      <c r="F54" s="6"/>
+      <c r="F54" s="9" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="7"/>
-      <c r="B55" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D55" s="5" t="n">
+      <c r="B55" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D55" s="8" t="n">
+        <v>101</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="F55" s="14" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="7"/>
+      <c r="B56" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D56" s="8" t="n">
+        <v>140</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2"/>
+      <c r="F57" s="2"/>
+    </row>
+    <row r="58" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="22"/>
+      <c r="B58" s="23" t="s">
+        <v>155</v>
+      </c>
+      <c r="C58" s="19"/>
+      <c r="D58" s="19"/>
+      <c r="E58" s="19"/>
+      <c r="F58" s="20"/>
+    </row>
+    <row r="59" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="7"/>
+      <c r="B59" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D59" s="8" t="n">
+        <v>146</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="7"/>
+      <c r="B60" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" s="8" t="n">
+        <v>146</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="7"/>
+      <c r="B61" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="C61" s="8"/>
+      <c r="D61" s="8"/>
+      <c r="E61" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="7"/>
+      <c r="B62" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="C62" s="8"/>
+      <c r="D62" s="8"/>
+      <c r="E62" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="F62" s="9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="7"/>
+      <c r="B63" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D63" s="8" t="n">
+        <v>110</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="7"/>
+      <c r="B64" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="D64" s="8" t="n">
+        <v>142</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="F64" s="9" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="7"/>
+      <c r="B65" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D65" s="8" t="n">
+        <v>97</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="7"/>
+      <c r="B66" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="E55" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="F55" s="6" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4"/>
-      <c r="B56" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D56" s="5" t="n">
-        <v>83</v>
-      </c>
-      <c r="E56" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="F56" s="6" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="4"/>
-      <c r="B57" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D57" s="5" t="n">
-        <v>110</v>
-      </c>
-      <c r="E57" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="F57" s="6" t="s">
+      <c r="C66" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D66" s="8" t="n">
+        <v>117</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F66" s="9" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="7"/>
+      <c r="B67" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D67" s="8" t="n">
+        <v>131</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="7"/>
+      <c r="B68" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D68" s="8" t="n">
+        <v>163</v>
+      </c>
+      <c r="E68" s="8" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="58" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="4"/>
-      <c r="B58" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="C58" s="5"/>
-      <c r="D58" s="5" t="n">
-        <v>140</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="F58" s="6" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="2"/>
-      <c r="F59" s="2"/>
-    </row>
-    <row r="60" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="22"/>
-      <c r="B60" s="23" t="s">
-        <v>161</v>
-      </c>
-      <c r="C60" s="19"/>
-      <c r="D60" s="19"/>
-      <c r="E60" s="19"/>
-      <c r="F60" s="20"/>
-    </row>
-    <row r="61" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="4"/>
-      <c r="B61" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="D61" s="5"/>
-      <c r="E61" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="F61" s="6" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="4"/>
-      <c r="B62" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D62" s="5" t="n">
-        <v>146</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="F62" s="6" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="4"/>
-      <c r="B63" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D63" s="5" t="n">
-        <v>146</v>
-      </c>
-      <c r="E63" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F63" s="6" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="4"/>
-      <c r="B64" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="C64" s="5"/>
-      <c r="D64" s="5"/>
-      <c r="E64" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="F64" s="6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="4"/>
-      <c r="B65" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D65" s="5" t="n">
-        <v>134</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F65" s="6" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="4"/>
-      <c r="B66" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="D66" s="5" t="n">
-        <v>142</v>
-      </c>
-      <c r="E66" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="F66" s="6" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="4"/>
-      <c r="B67" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D67" s="5" t="n">
-        <v>97</v>
-      </c>
-      <c r="E67" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="F67" s="6" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="4"/>
-      <c r="B68" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D68" s="5" t="n">
-        <v>117</v>
-      </c>
-      <c r="E68" s="5" t="s">
+      <c r="F68" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="F68" s="6" t="s">
-        <v>145</v>
-      </c>
     </row>
     <row r="69" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="4"/>
-      <c r="B69" s="5" t="s">
+      <c r="A69" s="7"/>
+      <c r="B69" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="C69" s="5"/>
-      <c r="D69" s="5"/>
-      <c r="E69" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="F69" s="6" t="s">
+      <c r="C69" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D69" s="8" t="n">
+        <v>101</v>
+      </c>
+      <c r="E69" s="8"/>
+      <c r="F69" s="9" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="4"/>
-      <c r="B70" s="5" t="s">
+      <c r="A70" s="7"/>
+      <c r="B70" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="C70" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D70" s="5" t="n">
-        <v>131</v>
-      </c>
-      <c r="E70" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F70" s="6" t="s">
+      <c r="C70" s="8"/>
+      <c r="D70" s="8"/>
+      <c r="E70" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F70" s="9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="7"/>
+      <c r="B71" s="8" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="71" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="4"/>
-      <c r="B71" s="5" t="s">
+      <c r="C71" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="D71" s="8" t="n">
+        <v>111</v>
+      </c>
+      <c r="E71" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F71" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="C71" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D71" s="5" t="n">
-        <v>163</v>
-      </c>
-      <c r="E71" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="F71" s="6" t="s">
+    </row>
+    <row r="72" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="7"/>
+      <c r="B72" s="8" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="72" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="4"/>
-      <c r="B72" s="5" t="s">
+      <c r="C72" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D72" s="8" t="n">
+        <v>115</v>
+      </c>
+      <c r="E72" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="C72" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D72" s="5" t="n">
-        <v>101</v>
-      </c>
-      <c r="E72" s="5"/>
-      <c r="F72" s="6" t="s">
+      <c r="F72" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="7"/>
+      <c r="B73" s="8" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="73" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="4"/>
-      <c r="B73" s="5" t="s">
+      <c r="C73" s="8"/>
+      <c r="D73" s="8"/>
+      <c r="E73" s="8"/>
+      <c r="F73" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="C73" s="5"/>
-      <c r="D73" s="5"/>
-      <c r="E73" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="F73" s="6" t="s">
-        <v>95</v>
-      </c>
     </row>
     <row r="74" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="4"/>
-      <c r="B74" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="D74" s="5" t="n">
-        <v>111</v>
-      </c>
-      <c r="E74" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F74" s="6" t="s">
-        <v>190</v>
-      </c>
+      <c r="A74" s="2"/>
+      <c r="F74" s="2"/>
     </row>
     <row r="75" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="4"/>
-      <c r="B75" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="C75" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D75" s="5" t="n">
-        <v>115</v>
-      </c>
-      <c r="E75" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="F75" s="6" t="s">
-        <v>74</v>
-      </c>
+      <c r="A75" s="2"/>
+      <c r="F75" s="2"/>
     </row>
     <row r="76" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="4"/>
-      <c r="B76" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="C76" s="5"/>
-      <c r="D76" s="5"/>
-      <c r="E76" s="5"/>
-      <c r="F76" s="6" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="4"/>
-      <c r="B77" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C77" s="5"/>
-      <c r="D77" s="5"/>
-      <c r="E77" s="5"/>
-      <c r="F77" s="6" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="4"/>
-      <c r="B78" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="C78" s="5"/>
-      <c r="D78" s="5"/>
-      <c r="E78" s="5"/>
-      <c r="F78" s="6" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="2"/>
-      <c r="F79" s="2"/>
-    </row>
-    <row r="80" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="2"/>
-      <c r="F80" s="2"/>
-    </row>
-    <row r="81" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="2"/>
-      <c r="F81" s="2"/>
-    </row>
+      <c r="A76" s="2"/>
+      <c r="F76" s="2"/>
+    </row>
+    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -2640,188 +2510,187 @@
   <sheetData>
     <row r="1" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="24" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D1" s="25"/>
     </row>
     <row r="2" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="26" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="B3" s="28" t="s">
-        <v>203</v>
-      </c>
-      <c r="C3" s="29" t="s">
-        <v>204</v>
+        <v>193</v>
+      </c>
+      <c r="B3" s="27" t="s">
+        <v>194</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="26" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="26" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="C5" s="26" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="C6" s="26" t="s">
         <v>116</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="27" t="s">
-        <v>208</v>
-      </c>
-      <c r="C6" s="26" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="26" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="26" t="s">
-        <v>211</v>
-      </c>
-      <c r="B8" s="30" t="s">
-        <v>76</v>
+        <v>202</v>
+      </c>
+      <c r="B8" s="29" t="s">
+        <v>74</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="26" t="s">
-        <v>213</v>
-      </c>
-      <c r="B9" s="30" t="s">
-        <v>79</v>
+        <v>204</v>
+      </c>
+      <c r="B9" s="29" t="s">
+        <v>77</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="26" t="s">
-        <v>214</v>
-      </c>
-      <c r="B10" s="30" t="s">
-        <v>81</v>
+        <v>205</v>
+      </c>
+      <c r="B10" s="29" t="s">
+        <v>79</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>130</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" s="29" t="s">
-        <v>84</v>
+        <v>35</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>82</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="26" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>218</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="26" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>137</v>
+        <v>212</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="26" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>225</v>
-      </c>
-      <c r="C16" s="26" t="s">
-        <v>226</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
     </row>
     <row r="17" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="31"/>
       <c r="B17" s="26" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/setlists/Stove Up.xlsx
+++ b/setlists/Stove Up.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="209">
   <si>
     <t xml:space="preserve">SET 1</t>
   </si>
@@ -518,9 +518,6 @@
     <t xml:space="preserve">Doobie Brothers</t>
   </si>
   <si>
-    <t xml:space="preserve">Cinnamon Girl</t>
-  </si>
-  <si>
     <t xml:space="preserve">Desire</t>
   </si>
   <si>
@@ -539,18 +536,6 @@
     <t xml:space="preserve">Better Than Ezra</t>
   </si>
   <si>
-    <t xml:space="preserve">Green River</t>
-  </si>
-  <si>
-    <t xml:space="preserve">??</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E7 C A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCR</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hold the Line</t>
   </si>
   <si>
@@ -563,24 +548,12 @@
     <t xml:space="preserve">F C Am G</t>
   </si>
   <si>
-    <t xml:space="preserve">Let's Go</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Cars</t>
-  </si>
-  <si>
     <t xml:space="preserve">Paranoid</t>
   </si>
   <si>
     <t xml:space="preserve">Black Sabbath</t>
   </si>
   <si>
-    <t xml:space="preserve">Possum Kingdom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toadies</t>
-  </si>
-  <si>
     <t xml:space="preserve">Run To You</t>
   </si>
   <si>
@@ -594,12 +567,6 @@
   </si>
   <si>
     <t xml:space="preserve">C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two Tickets To Paradise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eddie Money</t>
   </si>
   <si>
     <t xml:space="preserve">Set 1</t>
@@ -2258,224 +2225,151 @@
       <c r="C61" s="8"/>
       <c r="D61" s="8"/>
       <c r="E61" s="8" t="s">
-        <v>129</v>
+        <v>162</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>68</v>
+        <v>163</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="7"/>
       <c r="B62" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="C62" s="8"/>
-      <c r="D62" s="8"/>
+        <v>164</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D62" s="8" t="n">
+        <v>110</v>
+      </c>
       <c r="E62" s="8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="7"/>
       <c r="B63" s="8" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D63" s="8" t="n">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>166</v>
+        <v>58</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="7"/>
       <c r="B64" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>169</v>
+        <v>6</v>
       </c>
       <c r="D64" s="8" t="n">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="E64" s="8" t="s">
         <v>170</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>171</v>
+        <v>140</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="7"/>
       <c r="B65" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C65" s="8" t="s">
         <v>6</v>
       </c>
       <c r="D65" s="8" t="n">
-        <v>97</v>
+        <v>163</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>58</v>
+        <v>157</v>
       </c>
       <c r="F65" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="7"/>
       <c r="B66" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="C66" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D66" s="8" t="n">
-        <v>117</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="C66" s="8"/>
+      <c r="D66" s="8"/>
       <c r="E66" s="8" t="s">
-        <v>175</v>
+        <v>58</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>140</v>
+        <v>93</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="7"/>
       <c r="B67" s="8" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>6</v>
+        <v>133</v>
       </c>
       <c r="D67" s="8" t="n">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="E67" s="8" t="s">
         <v>10</v>
       </c>
       <c r="F67" s="9" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="7"/>
       <c r="B68" s="8" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C68" s="8" t="s">
         <v>6</v>
       </c>
       <c r="D68" s="8" t="n">
-        <v>163</v>
+        <v>115</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="F68" s="9" t="s">
-        <v>179</v>
+        <v>72</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="7"/>
-      <c r="B69" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="C69" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D69" s="8" t="n">
-        <v>101</v>
-      </c>
-      <c r="E69" s="8"/>
-      <c r="F69" s="9" t="s">
-        <v>181</v>
-      </c>
+      <c r="A69" s="2"/>
+      <c r="F69" s="2"/>
     </row>
     <row r="70" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="7"/>
-      <c r="B70" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="C70" s="8"/>
-      <c r="D70" s="8"/>
-      <c r="E70" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F70" s="9" t="s">
-        <v>93</v>
-      </c>
+      <c r="A70" s="2"/>
+      <c r="F70" s="2"/>
     </row>
     <row r="71" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="7"/>
-      <c r="B71" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="C71" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="D71" s="8" t="n">
-        <v>111</v>
-      </c>
-      <c r="E71" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F71" s="9" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="7"/>
-      <c r="B72" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="C72" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D72" s="8" t="n">
-        <v>115</v>
-      </c>
-      <c r="E72" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="F72" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="7"/>
-      <c r="B73" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="C73" s="8"/>
-      <c r="D73" s="8"/>
-      <c r="E73" s="8"/>
-      <c r="F73" s="9" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="2"/>
-      <c r="F74" s="2"/>
-    </row>
-    <row r="75" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="2"/>
-      <c r="F75" s="2"/>
-    </row>
-    <row r="76" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="2"/>
-      <c r="F76" s="2"/>
-    </row>
+      <c r="A71" s="2"/>
+      <c r="F71" s="2"/>
+    </row>
+    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -2510,13 +2404,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="24" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="D1" s="25"/>
     </row>
@@ -2525,7 +2419,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="C2" s="26" t="s">
         <v>104</v>
@@ -2533,18 +2427,18 @@
     </row>
     <row r="3" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="26" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="26" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="B4" s="27" t="s">
         <v>60</v>
@@ -2555,10 +2449,10 @@
     </row>
     <row r="5" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="26" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="C5" s="26" t="s">
         <v>113</v>
@@ -2569,7 +2463,7 @@
         <v>20</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="C6" s="26" t="s">
         <v>116</v>
@@ -2577,10 +2471,10 @@
     </row>
     <row r="7" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="26" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="C7" s="26" t="s">
         <v>119</v>
@@ -2588,18 +2482,18 @@
     </row>
     <row r="8" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="26" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="B8" s="29" t="s">
         <v>74</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="26" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="B9" s="29" t="s">
         <v>77</v>
@@ -2610,13 +2504,13 @@
     </row>
     <row r="10" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="26" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="B10" s="29" t="s">
         <v>79</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2627,15 +2521,15 @@
         <v>82</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="26" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="C12" s="26" t="s">
         <v>132</v>
@@ -2643,13 +2537,13 @@
     </row>
     <row r="13" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="26" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2660,18 +2554,18 @@
         <v>91</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="26" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2679,7 +2573,7 @@
         <v>49</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="C16" s="30"/>
       <c r="D16" s="30"/>
@@ -2687,10 +2581,10 @@
     <row r="17" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="31"/>
       <c r="B17" s="26" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/setlists/Stove Up.xlsx
+++ b/setlists/Stove Up.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="203">
   <si>
     <t xml:space="preserve">SET 1</t>
   </si>
@@ -277,13 +277,10 @@
     <t xml:space="preserve">Std</t>
   </si>
   <si>
-    <t xml:space="preserve">* Ivory Solo *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Any solo while we go std</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tenacious D</t>
+    <t xml:space="preserve">* Ivory Filibuster *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tuning change</t>
   </si>
   <si>
     <t xml:space="preserve">Working For the Weekend ↓</t>
@@ -295,16 +292,7 @@
     <t xml:space="preserve">Loverboy</t>
   </si>
   <si>
-    <t xml:space="preserve">Semi Charmed Life</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G D C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Third Eye Blind</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summer of '69 ↓</t>
+    <t xml:space="preserve">Summer of '69</t>
   </si>
   <si>
     <t xml:space="preserve">V: D A – Bm A D G
@@ -323,7 +311,16 @@
     <t xml:space="preserve">Harvey Danger</t>
   </si>
   <si>
-    <t xml:space="preserve">My Own Worst Enemy ↓</t>
+    <t xml:space="preserve">She's A Beauty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K+I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Tubes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Own Worst Enemy</t>
   </si>
   <si>
     <t xml:space="preserve">E F# A B</t>
@@ -363,6 +360,115 @@
     <t xml:space="preserve">Kiss</t>
   </si>
   <si>
+    <t xml:space="preserve">Hold the Line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crackerman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A B, E F#, B: F# A D E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aeroplane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gm – C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RHCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inside Out ↓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C: A E F# - A E B -(E B F#)
+V: B F# A G B F# E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eve 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumbersome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F#</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seven Mary Three</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beast of Burden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E B C#m A – A E/G# A B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Movin' Out ↓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dm – ends on D Major</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billy Joel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">American Band ↓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grand Funk Railroad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">December ↓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G F C Bb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santa Monica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Everclear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D C E G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cracker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mary Jane's Last Dance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V: Am G D Am  C: D A  G, Harp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Petty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Champagne Supernova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oasis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other</t>
+  </si>
+  <si>
     <t xml:space="preserve">Blitzkreig Bop</t>
   </si>
   <si>
@@ -373,200 +479,73 @@
     <t xml:space="preserve">Ramones</t>
   </si>
   <si>
-    <t xml:space="preserve">Crackerman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A B, E F#, B: F# A D E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aeroplane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gm – C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RHCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inside Out ↓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C: A E F# - A E B -(E B F#)
-V: B F# A G B F# E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eve 6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cumbersome</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F#</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seven Mary Three</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Movin' Out ↓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dm – ends on D Major</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billy Joel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">American Band ↓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grand Funk Railroad</t>
+    <t xml:space="preserve">Cinnamon Girl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Come Together</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V: Dm A G  C: Bm G A Dm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beatles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V:G D Em C S: A E F#m D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Better Than Ezra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Love Song</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V: Am9 G F G C: F G Am C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Cure</t>
   </si>
   <si>
     <t xml:space="preserve">Hey Jealousy</t>
   </si>
   <si>
-    <t xml:space="preserve">December ↓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K+I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G F C Bb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santa Monica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Everclear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mary Jane's Last Dance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V: Am G D Am  C: D A  G, Harp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Petty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Champagne Supernova</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oasis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D C E G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cracker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Come Together</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V: Dm A G  C: Bm G A Dm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beatles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beast of Burden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E B C#m A – A E/G# A B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Love Song</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V: Am9 G F G C: F G Am C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Cure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Misc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Born to Be Wild</t>
+    <t xml:space="preserve">Paranoid</t>
   </si>
   <si>
     <t xml:space="preserve">E</t>
   </si>
   <si>
-    <t xml:space="preserve">Steppenwolf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">China Grove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doobie Brothers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E (in standard for harp)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Good</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V:G D Em C S: A E F#m D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Better Than Ezra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hold the Line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning To Fly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F C Am G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paranoid</t>
-  </si>
-  <si>
     <t xml:space="preserve">Black Sabbath</t>
   </si>
   <si>
+    <t xml:space="preserve">Power Of Love</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E / Bm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huey Lewis</t>
+  </si>
+  <si>
     <t xml:space="preserve">Run To You</t>
   </si>
   <si>
-    <t xml:space="preserve">She's A Beauty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Tubes</t>
-  </si>
-  <si>
     <t xml:space="preserve">Shimmer</t>
   </si>
   <si>
     <t xml:space="preserve">C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semi Charmed Life</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G D C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Third Eye Blind</t>
   </si>
   <si>
     <t xml:space="preserve">Set 1</t>
@@ -623,6 +602,9 @@
     <t xml:space="preserve"> - All Right Now ↓</t>
   </si>
   <si>
+    <t xml:space="preserve">Hold The Line</t>
+  </si>
+  <si>
     <t xml:space="preserve"> - Fire on Mountain</t>
   </si>
   <si>
@@ -647,49 +629,49 @@
     <t xml:space="preserve"> - All For You ↓</t>
   </si>
   <si>
+    <t xml:space="preserve">Beast Of Burden</t>
+  </si>
+  <si>
     <t xml:space="preserve"> - Mr Jones &amp; Me</t>
   </si>
   <si>
+    <t xml:space="preserve">* Filibuster *</t>
+  </si>
+  <si>
     <t xml:space="preserve"> - American Band ↓</t>
   </si>
   <si>
-    <t xml:space="preserve"> - Hey Jealousy</t>
-  </si>
-  <si>
     <t xml:space="preserve"> - Long Way Down ↓</t>
   </si>
   <si>
-    <t xml:space="preserve">Working For Week ↓</t>
+    <t xml:space="preserve">Working For Week</t>
   </si>
   <si>
     <t xml:space="preserve"> - Counting Blue Cars</t>
   </si>
   <si>
-    <t xml:space="preserve"> - Semi-Charmed</t>
-  </si>
-  <si>
     <t xml:space="preserve"> - Santa Monica</t>
   </si>
   <si>
+    <t xml:space="preserve"> - Bad Case of Loving</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> She’s A Beauty</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mary Jane's Last</t>
   </si>
   <si>
-    <t xml:space="preserve"> - Bad Case of Loving</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Flagpole Sitta</t>
+    <t xml:space="preserve">My Own Worst En ↓</t>
   </si>
   <si>
     <t xml:space="preserve">Champ Supernova</t>
   </si>
   <si>
-    <t xml:space="preserve">My Own Worst En ↓</t>
-  </si>
-  <si>
     <t xml:space="preserve"> - Don't You Forget</t>
   </si>
   <si>
-    <t xml:space="preserve">Beast_o_B, Low, Come Together, Lovesong</t>
+    <t xml:space="preserve">Blitz, Jealousy, Lovesong,</t>
   </si>
 </sst>
 </file>
@@ -699,7 +681,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="15">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -745,13 +727,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFFB66C"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -973,47 +948,47 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1689,20 +1664,16 @@
       <c r="C28" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D28" s="8" t="n">
-        <v>119</v>
-      </c>
+      <c r="D28" s="8"/>
       <c r="E28" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="F28" s="9" t="s">
-        <v>84</v>
-      </c>
+      <c r="F28" s="9"/>
     </row>
     <row r="29" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="10"/>
       <c r="B29" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>6</v>
@@ -1711,70 +1682,70 @@
         <v>147</v>
       </c>
       <c r="E29" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="F29" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="F29" s="9" t="s">
+    </row>
+    <row r="30" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4"/>
+      <c r="B30" s="8" t="s">
         <v>87</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="10"/>
-      <c r="B30" s="8" t="s">
-        <v>88</v>
       </c>
       <c r="C30" s="8" t="s">
         <v>6</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="E30" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="F30" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="F30" s="9" t="s">
+    </row>
+    <row r="31" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4"/>
+      <c r="B31" s="8" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="11"/>
-      <c r="B31" s="8" t="s">
+      <c r="C31" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>145</v>
+      </c>
+      <c r="E31" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="C31" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D31" s="8" t="n">
-        <v>139</v>
-      </c>
-      <c r="E31" s="8" t="s">
+      <c r="F31" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="F31" s="9" t="s">
+    </row>
+    <row r="32" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7"/>
+      <c r="B32" s="8" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="11"/>
-      <c r="B32" s="8" t="s">
+      <c r="C32" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="C32" s="8" t="s">
-        <v>13</v>
-      </c>
       <c r="D32" s="8" t="n">
-        <v>145</v>
+        <v>111</v>
       </c>
       <c r="E32" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" s="9" t="s">
         <v>95</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>6</v>
@@ -1783,16 +1754,16 @@
         <v>103</v>
       </c>
       <c r="E33" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="F33" s="9" t="s">
         <v>98</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="10"/>
       <c r="B34" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>17</v>
@@ -1801,10 +1772,10 @@
         <v>111</v>
       </c>
       <c r="E34" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="F34" s="9" t="s">
         <v>101</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1818,7 +1789,7 @@
     <row r="36" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="4"/>
       <c r="B36" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
@@ -1828,7 +1799,7 @@
     <row r="37" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="10"/>
       <c r="B37" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>6</v>
@@ -1837,16 +1808,16 @@
         <v>110</v>
       </c>
       <c r="E37" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="F37" s="9" t="s">
         <v>105</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="10"/>
       <c r="B38" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C38" s="8" t="s">
         <v>13</v>
@@ -1855,34 +1826,34 @@
         <v>128</v>
       </c>
       <c r="E38" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F38" s="9" t="s">
         <v>108</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="7"/>
       <c r="B39" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>97</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F39" s="9" t="s">
         <v>110</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D39" s="8" t="n">
-        <v>177</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="7"/>
       <c r="B40" s="8" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C40" s="8" t="s">
         <v>6</v>
@@ -1891,16 +1862,16 @@
         <v>149</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="7"/>
       <c r="B41" s="8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>13</v>
@@ -1909,16 +1880,16 @@
         <v>101</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="10"/>
       <c r="B42" s="8" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C42" s="8" t="s">
         <v>6</v>
@@ -1927,16 +1898,16 @@
         <v>176</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="10"/>
       <c r="B43" s="8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C43" s="8" t="s">
         <v>13</v>
@@ -1945,79 +1916,79 @@
         <v>81</v>
       </c>
       <c r="E43" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="7"/>
+      <c r="B44" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="F43" s="9" t="s">
+      <c r="C44" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>101</v>
+      </c>
+      <c r="E44" s="8" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="44" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="10"/>
-      <c r="B44" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D44" s="8" t="n">
-        <v>134</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="F44" s="9" t="s">
-        <v>127</v>
+      <c r="F44" s="14" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="10"/>
       <c r="B45" s="8" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C45" s="8" t="s">
         <v>13</v>
       </c>
       <c r="D45" s="8" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="10"/>
       <c r="B46" s="8" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D46" s="8" t="n">
-        <v>153</v>
+        <v>128</v>
       </c>
       <c r="E46" s="8" t="s">
         <v>129</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="11"/>
       <c r="B47" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>133</v>
+        <v>94</v>
       </c>
       <c r="D47" s="8" t="n">
         <v>122</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>80</v>
@@ -2026,7 +1997,7 @@
     <row r="48" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="11"/>
       <c r="B48" s="8" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C48" s="8" t="s">
         <v>13</v>
@@ -2035,168 +2006,182 @@
         <v>100</v>
       </c>
       <c r="E48" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="4"/>
+      <c r="B49" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="F48" s="9" t="s">
+      <c r="C49" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D49" s="8" t="n">
+        <v>174</v>
+      </c>
+      <c r="E49" s="8" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="49" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="7"/>
-      <c r="B49" s="8" t="s">
+      <c r="F49" s="9" t="s">
         <v>138</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D49" s="8" t="n">
-        <v>85</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="F49" s="9" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="7"/>
       <c r="B50" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C50" s="8" t="s">
         <v>6</v>
       </c>
       <c r="D50" s="8" t="n">
+        <v>85</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="7"/>
+      <c r="B51" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D51" s="8" t="n">
         <v>150</v>
       </c>
-      <c r="E50" s="8" t="s">
+      <c r="E51" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F50" s="9" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0"/>
-      <c r="B51" s="0"/>
-      <c r="C51" s="0"/>
-      <c r="D51" s="0"/>
-      <c r="E51" s="0"/>
-      <c r="F51" s="0"/>
+      <c r="F51" s="9" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="7"/>
-      <c r="B52" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="C52" s="8"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="9"/>
+      <c r="A52" s="2"/>
+      <c r="F52" s="2"/>
     </row>
     <row r="53" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4"/>
-      <c r="B53" s="8" t="s">
+      <c r="A53" s="7"/>
+      <c r="B53" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="C53" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D53" s="8" t="n">
-        <v>174</v>
-      </c>
-      <c r="E53" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="F53" s="9" t="s">
-        <v>146</v>
-      </c>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="9"/>
     </row>
     <row r="54" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="7"/>
       <c r="B54" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C54" s="8" t="s">
         <v>13</v>
       </c>
       <c r="D54" s="8" t="n">
-        <v>83</v>
+        <v>177</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="7"/>
       <c r="B55" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="C55" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D55" s="8" t="n">
-        <v>101</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="C55" s="8"/>
+      <c r="D55" s="8"/>
       <c r="E55" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="F55" s="14" t="s">
-        <v>106</v>
+        <v>129</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="7"/>
       <c r="B56" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D56" s="8" t="n">
+        <v>83</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="7"/>
+      <c r="B57" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="C56" s="8" t="s">
+      <c r="C57" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D57" s="8" t="n">
+        <v>110</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="7"/>
+      <c r="B58" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="C58" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D56" s="8" t="n">
+      <c r="D58" s="8" t="n">
         <v>140</v>
       </c>
-      <c r="E56" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="F56" s="9" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="2"/>
-      <c r="F57" s="2"/>
-    </row>
-    <row r="58" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="22"/>
-      <c r="B58" s="23" t="s">
-        <v>155</v>
-      </c>
-      <c r="C58" s="19"/>
-      <c r="D58" s="19"/>
-      <c r="E58" s="19"/>
-      <c r="F58" s="20"/>
+      <c r="E58" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="7"/>
       <c r="B59" s="8" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C59" s="8" t="s">
         <v>6</v>
       </c>
       <c r="D59" s="8" t="n">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>157</v>
+        <v>129</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>158</v>
+        <v>28</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2205,166 +2190,97 @@
         <v>159</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D60" s="8" t="n">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>45</v>
+        <v>160</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="7"/>
       <c r="B61" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="C61" s="8"/>
+        <v>162</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>17</v>
+      </c>
       <c r="D61" s="8"/>
       <c r="E61" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="7"/>
       <c r="B62" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D62" s="8" t="n">
-        <v>110</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="C62" s="8"/>
+      <c r="D62" s="8"/>
       <c r="E62" s="8" t="s">
-        <v>165</v>
+        <v>58</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>166</v>
+        <v>89</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="7"/>
       <c r="B63" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C63" s="8" t="s">
         <v>6</v>
       </c>
       <c r="D63" s="8" t="n">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>58</v>
+        <v>167</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>168</v>
+        <v>72</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="7"/>
       <c r="B64" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C64" s="8" t="s">
         <v>6</v>
       </c>
       <c r="D64" s="8" t="n">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="E64" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="F64" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="F64" s="9" t="s">
-        <v>140</v>
-      </c>
     </row>
     <row r="65" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="7"/>
-      <c r="B65" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="C65" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D65" s="8" t="n">
-        <v>163</v>
-      </c>
-      <c r="E65" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="F65" s="9" t="s">
-        <v>172</v>
-      </c>
+      <c r="A65" s="2"/>
+      <c r="F65" s="2"/>
     </row>
     <row r="66" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="7"/>
-      <c r="B66" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="C66" s="8"/>
-      <c r="D66" s="8"/>
-      <c r="E66" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F66" s="9" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="7"/>
-      <c r="B67" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="C67" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="D67" s="8" t="n">
-        <v>111</v>
-      </c>
-      <c r="E67" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F67" s="9" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="7"/>
-      <c r="B68" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D68" s="8" t="n">
-        <v>115</v>
-      </c>
-      <c r="E68" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="F68" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="2"/>
-      <c r="F69" s="2"/>
-    </row>
-    <row r="70" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="2"/>
-      <c r="F70" s="2"/>
-    </row>
-    <row r="71" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="2"/>
-      <c r="F71" s="2"/>
-    </row>
+      <c r="A66" s="2"/>
+      <c r="F66" s="2"/>
+    </row>
+    <row r="1048559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -2403,191 +2319,195 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="22" t="s">
+        <v>171</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>173</v>
+      </c>
+      <c r="D1" s="23"/>
+    </row>
+    <row r="2" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="24" t="s">
         <v>178</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B4" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="24" t="s">
         <v>179</v>
       </c>
-      <c r="C1" s="24" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="D1" s="25"/>
-    </row>
-    <row r="2" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="26" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="27" t="s">
+      <c r="B5" s="25" t="s">
         <v>181</v>
       </c>
-      <c r="C2" s="26" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="26" t="s">
+      <c r="C5" s="24" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="25" t="s">
         <v>182</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="C6" s="24" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="24" t="s">
         <v>183</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="B7" s="25" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="26" t="s">
+      <c r="C7" s="24" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="24" t="s">
         <v>185</v>
       </c>
-      <c r="B4" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" s="26" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="26" t="s">
+      <c r="B8" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="24" t="s">
         <v>186</v>
       </c>
-      <c r="B5" s="27" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="24" t="s">
         <v>187</v>
       </c>
-      <c r="C5" s="26" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="27" t="s">
+      <c r="B9" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="28" t="s">
         <v>188</v>
       </c>
-      <c r="C6" s="26" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="26" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="24" t="s">
         <v>189</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="B10" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="26" t="s">
         <v>190</v>
       </c>
-      <c r="C7" s="26" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="26" t="s">
+      <c r="C11" s="24" t="s">
         <v>191</v>
       </c>
-      <c r="B8" s="29" t="s">
-        <v>74</v>
-      </c>
-      <c r="C8" s="26" t="s">
+    </row>
+    <row r="12" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="24" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="26" t="s">
+      <c r="B12" s="24" t="s">
         <v>193</v>
       </c>
-      <c r="B9" s="29" t="s">
-        <v>77</v>
-      </c>
-      <c r="C9" s="26" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="26" t="s">
+      <c r="C12" s="24" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="24" t="s">
         <v>194</v>
       </c>
-      <c r="B10" s="29" t="s">
-        <v>79</v>
-      </c>
-      <c r="C10" s="26" t="s">
+      <c r="B13" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" s="24" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" s="28" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" s="26" t="s">
+    <row r="14" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="24" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="26" t="s">
+      <c r="B15" s="29" t="s">
         <v>197</v>
       </c>
-      <c r="B12" s="26" t="s">
+      <c r="C15" s="24" t="s">
         <v>198</v>
       </c>
-      <c r="C12" s="26" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="26" t="s">
+    </row>
+    <row r="16" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="24" t="s">
         <v>199</v>
       </c>
-      <c r="B13" s="26" t="s">
+      <c r="C16" s="24" t="s">
         <v>200</v>
       </c>
-      <c r="C13" s="26" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="B14" s="26" t="s">
-        <v>91</v>
-      </c>
-      <c r="C14" s="26" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="26" t="s">
-        <v>203</v>
-      </c>
-      <c r="B15" s="26" t="s">
-        <v>204</v>
-      </c>
-      <c r="C15" s="26" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="B16" s="26" t="s">
-        <v>206</v>
-      </c>
-      <c r="C16" s="30"/>
       <c r="D16" s="30"/>
     </row>
     <row r="17" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="31"/>
-      <c r="B17" s="26" t="s">
-        <v>207</v>
+      <c r="B17" s="24" t="s">
+        <v>201</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+        <v>202</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C18" s="0"/>
+    </row>
     <row r="19" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="20" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>

--- a/setlists/Stove Up.xlsx
+++ b/setlists/Stove Up.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="1" state="visible" r:id="rId3"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="202">
   <si>
     <t xml:space="preserve">SET 1</t>
   </si>
@@ -629,9 +629,6 @@
     <t xml:space="preserve"> - All For You ↓</t>
   </si>
   <si>
-    <t xml:space="preserve">Beast Of Burden</t>
-  </si>
-  <si>
     <t xml:space="preserve"> - Mr Jones &amp; Me</t>
   </si>
   <si>
@@ -681,7 +678,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="14">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -762,12 +759,6 @@
     </font>
     <font>
       <sz val="16"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="16"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -859,7 +850,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -972,23 +963,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2414,13 +2397,13 @@
       <c r="B9" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="C9" s="28" t="s">
-        <v>188</v>
+      <c r="C9" s="24" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="24" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B10" s="27" t="s">
         <v>79</v>
@@ -2434,18 +2417,18 @@
         <v>35</v>
       </c>
       <c r="B11" s="26" t="s">
+        <v>189</v>
+      </c>
+      <c r="C11" s="24" t="s">
         <v>190</v>
-      </c>
-      <c r="C11" s="24" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="24" t="s">
+        <v>191</v>
+      </c>
+      <c r="B12" s="24" t="s">
         <v>192</v>
-      </c>
-      <c r="B12" s="24" t="s">
-        <v>193</v>
       </c>
       <c r="C12" s="24" t="s">
         <v>131</v>
@@ -2453,13 +2436,13 @@
     </row>
     <row r="13" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="24" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B13" s="24" t="s">
         <v>87</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2469,19 +2452,19 @@
       <c r="B14" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="C14" s="28" t="s">
+      <c r="C14" s="24" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="24" t="s">
+        <v>195</v>
+      </c>
+      <c r="B15" s="24" t="s">
         <v>196</v>
       </c>
-      <c r="B15" s="29" t="s">
+      <c r="C15" s="24" t="s">
         <v>197</v>
-      </c>
-      <c r="C15" s="24" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2489,25 +2472,23 @@
         <v>49</v>
       </c>
       <c r="B16" s="24" t="s">
+        <v>198</v>
+      </c>
+      <c r="C16" s="24" t="s">
         <v>199</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="D16" s="28"/>
+    </row>
+    <row r="17" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="29"/>
+      <c r="B17" s="24" t="s">
         <v>200</v>
       </c>
-      <c r="D16" s="30"/>
-    </row>
-    <row r="17" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="31"/>
-      <c r="B17" s="24" t="s">
+      <c r="C17" s="30" t="s">
         <v>201</v>
       </c>
-      <c r="C17" s="32" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C18" s="0"/>
-    </row>
+    </row>
+    <row r="18" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="19" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="20" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>

--- a/setlists/Stove Up.xlsx
+++ b/setlists/Stove Up.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="212">
   <si>
     <t xml:space="preserve">SET 1</t>
   </si>
@@ -142,7 +142,7 @@
     <t xml:space="preserve">Bruce Springsteen</t>
   </si>
   <si>
-    <t xml:space="preserve">Long Way Down ↓</t>
+    <t xml:space="preserve">Long Way Down</t>
   </si>
   <si>
     <t xml:space="preserve">Bm </t>
@@ -292,305 +292,318 @@
     <t xml:space="preserve">Loverboy</t>
   </si>
   <si>
-    <t xml:space="preserve">Summer of '69</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V: D A – Bm A D G
-B: F Bb C Bb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bryan Adams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flagpole Sitta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V:D Am C D  B: A G F G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harvey Danger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">She's A Beauty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K+I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Tubes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My Own Worst Enemy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E F# A B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Don't You Forget About Me</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I: D E, D E C D,D E
-V: E D A D, B: C G D A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simple Minds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SET 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miss You ↓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Am Dm – F Em Dm – E#9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rolling Stones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Was Made For Lovin You</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Em – Am, (Em G B [Em/A])</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hold the Line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crackerman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A B, E F#, B: F# A D E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aeroplane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gm – C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RHCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inside Out ↓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C: A E F# - A E B -(E B F#)
-V: B F# A G B F# E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eve 6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cumbersome</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F#</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seven Mary Three</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beast of Burden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E B C#m A – A E/G# A B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Movin' Out ↓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dm – ends on D Major</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billy Joel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">American Band ↓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grand Funk Railroad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">December ↓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G F C Bb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santa Monica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Everclear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D C E G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cracker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mary Jane's Last Dance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V: Am G D Am  C: D A  G, Harp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Petty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Champagne Supernova</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oasis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blitzkreig Bop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V: (A D E) – A D A
-C:  D A D B D E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cinnamon Girl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Come Together</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V: Dm A G  C: Bm G A Dm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beatles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Good</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V:G D Em C S: A E F#m D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Better Than Ezra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Love Song</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V: Am9 G F G C: F G Am C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Cure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hey Jealousy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paranoid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Black Sabbath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Power Of Love</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E / Bm </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Huey Lewis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Run To You</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shimmer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Semi Charmed Life</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G D C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Third Eye Blind</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nothin’ But A Good ↓</t>
-  </si>
-  <si>
     <r>
       <rPr>
-        <sz val="16"/>
+        <sz val="11"/>
         <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">A Girl Like You</t>
+      <t xml:space="preserve">Summer of '69</t>
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="16"/>
+        <sz val="11"/>
         <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve"> ↓</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">↓</t>
-    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">V: D A – Bm A D G
+B: F Bb C Bb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bryan Adams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flagpole Sitta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V:D Am C D  B: A G F G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harvey Danger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She's A Beauty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K+I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Tubes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Own Worst Enemy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E F# A B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Don't You Forget About Me</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I: D E, D E C D,D E
+V: E D A D, B: C G D A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simple Minds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SET 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miss You ↓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Am Dm – F Em Dm – E#9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rolling Stones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Was Made For Lovin You</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Em – Am, (Em G B [Em/A])</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hold the Line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crackerman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A B, E F#, B: F# A D E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aeroplane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gm – C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RHCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inside Out ↓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C: A E F# - A E B -(E B F#)
+V: B F# A G B F# E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eve 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumbersome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F#</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seven Mary Three</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beast of Burden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E B C#m A – A E/G# A B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Movin' Out ↓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dm – ends on D Major</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billy Joel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">American Band</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grand Funk Railroad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">December ↓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G F C Bb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santa Monica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Everclear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D C E G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cracker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mary Jane's Last Dance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V: Am G D Am  C: D A  G, Harp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Petty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Champagne Supernova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Harp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oasis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other / Ideas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billie Jean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Em -Am, (Em C) B7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michael Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blitzkreig Bop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V: (A D E) – A D A
+C:  D A D B D E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cinnamon Girl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Come Together</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V: Dm A G  C: Bm G A Dm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beatles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Franklin’s Tower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A G D
+Alt for Fire on The Mtn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V:G D Em C S: A E F#m D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Better Than Ezra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head Over Heels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tears For Fears</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Love Song</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V: Am9 G F G C: F G Am C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Cure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hey Jealousy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paranoid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black Sabbath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power Of Love</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E / Bm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huey Lewis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run To You</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shimmer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semi Charmed Life</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G D C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Third Eye Blind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nothin’ But A Good ↓</t>
   </si>
   <si>
     <t xml:space="preserve"> - Would?</t>
@@ -635,25 +648,31 @@
     <t xml:space="preserve">* Filibuster *</t>
   </si>
   <si>
-    <t xml:space="preserve"> - American Band ↓</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Long Way Down ↓</t>
+    <t xml:space="preserve"> - American Band</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Long Way Down</t>
   </si>
   <si>
     <t xml:space="preserve">Working For Week</t>
   </si>
   <si>
-    <t xml:space="preserve"> - Counting Blue Cars</t>
+    <t xml:space="preserve"> Counting Blue Cars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summer of '69 ↓</t>
   </si>
   <si>
     <t xml:space="preserve"> - Santa Monica</t>
   </si>
   <si>
+    <t xml:space="preserve"> - Flagpole Sitta</t>
+  </si>
+  <si>
     <t xml:space="preserve"> - Bad Case of Loving</t>
   </si>
   <si>
-    <t xml:space="preserve"> She’s A Beauty</t>
+    <t xml:space="preserve">She’s A Beauty</t>
   </si>
   <si>
     <t xml:space="preserve">Mary Jane's Last</t>
@@ -668,7 +687,7 @@
     <t xml:space="preserve"> - Don't You Forget</t>
   </si>
   <si>
-    <t xml:space="preserve">Blitz, Jealousy, Lovesong,</t>
+    <t xml:space="preserve">Blitz, Jealousy, Lovesong, Semi-Charm, Cinnamon</t>
   </si>
 </sst>
 </file>
@@ -729,6 +748,12 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="20"/>
       <color theme="1"/>
@@ -743,14 +768,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
       <sz val="16"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -939,31 +956,31 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1386,7 +1403,7 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11"/>
+      <c r="A13" s="7"/>
       <c r="B13" s="8" t="s">
         <v>41</v>
       </c>
@@ -1672,7 +1689,7 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4"/>
+      <c r="A30" s="11"/>
       <c r="B30" s="8" t="s">
         <v>87</v>
       </c>
@@ -1690,7 +1707,7 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4"/>
+      <c r="A31" s="11"/>
       <c r="B31" s="8" t="s">
         <v>90</v>
       </c>
@@ -2043,10 +2060,10 @@
         <v>150</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>10</v>
+        <v>143</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2056,7 +2073,7 @@
     <row r="53" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="7"/>
       <c r="B53" s="21" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C53" s="8"/>
       <c r="D53" s="8"/>
@@ -2064,204 +2081,253 @@
       <c r="F53" s="9"/>
     </row>
     <row r="54" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="7"/>
+      <c r="A54" s="7" t="s">
+        <v>146</v>
+      </c>
       <c r="B54" s="8" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D54" s="8" t="n">
-        <v>177</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="D54" s="8"/>
       <c r="E54" s="8" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="7"/>
       <c r="B55" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C55" s="8"/>
-      <c r="D55" s="8"/>
+        <v>150</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55" s="8" t="n">
+        <v>177</v>
+      </c>
       <c r="E55" s="8" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>68</v>
+        <v>152</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="7"/>
       <c r="B56" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>13</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="C56" s="8"/>
       <c r="D56" s="8" t="n">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>151</v>
+        <v>68</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="7"/>
       <c r="B57" s="8" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C57" s="8" t="s">
         <v>13</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>110</v>
+        <v>83</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="7"/>
       <c r="B58" s="8" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C58" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D58" s="8" t="n">
-        <v>140</v>
-      </c>
+      <c r="D58" s="8"/>
       <c r="E58" s="8" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>157</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="7"/>
       <c r="B59" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D59" s="8" t="n">
-        <v>153</v>
+        <v>110</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>129</v>
+        <v>160</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>28</v>
+        <v>161</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="7"/>
+      <c r="A60" s="7" t="s">
+        <v>146</v>
+      </c>
       <c r="B60" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="C60" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D60" s="8" t="n">
+        <v>162</v>
+      </c>
+      <c r="C60" s="8"/>
+      <c r="D60" s="8"/>
+      <c r="E60" s="8"/>
+      <c r="F60" s="9" t="s">
         <v>163</v>
-      </c>
-      <c r="E60" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="F60" s="9" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="7"/>
       <c r="B61" s="8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C61" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D61" s="8"/>
+      <c r="D61" s="8" t="n">
+        <v>140</v>
+      </c>
       <c r="E61" s="8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="7"/>
       <c r="B62" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="C62" s="8"/>
-      <c r="D62" s="8"/>
+        <v>167</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D62" s="8" t="n">
+        <v>153</v>
+      </c>
       <c r="E62" s="8" t="s">
-        <v>58</v>
+        <v>129</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>89</v>
+        <v>28</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="7"/>
       <c r="B63" s="8" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C63" s="8" t="s">
         <v>6</v>
       </c>
       <c r="D63" s="8" t="n">
-        <v>115</v>
+        <v>163</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>72</v>
+        <v>170</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="7"/>
       <c r="B64" s="8" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C64" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="D64" s="8"/>
+      <c r="E64" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="F64" s="9" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="7"/>
+      <c r="B65" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="C65" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D64" s="8" t="n">
+      <c r="D65" s="8"/>
+      <c r="E65" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="7"/>
+      <c r="B66" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D66" s="8" t="n">
+        <v>115</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="F66" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="7"/>
+      <c r="B67" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D67" s="8" t="n">
         <v>102</v>
       </c>
-      <c r="E64" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="F64" s="9" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="2"/>
-      <c r="F65" s="2"/>
-    </row>
-    <row r="66" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="2"/>
-      <c r="F66" s="2"/>
-    </row>
-    <row r="1048559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="E67" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="2"/>
+      <c r="F68" s="2"/>
+    </row>
+    <row r="69" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="2"/>
+      <c r="F69" s="2"/>
+    </row>
     <row r="1048562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -2303,13 +2369,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="22" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="D1" s="23"/>
     </row>
@@ -2318,7 +2384,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="C2" s="24" t="s">
         <v>103</v>
@@ -2326,32 +2392,32 @@
     </row>
     <row r="3" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="24" t="s">
-        <v>175</v>
+        <v>9</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="C3" s="26" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="24" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B4" s="25" t="s">
         <v>60</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="24" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C5" s="24" t="s">
         <v>111</v>
@@ -2362,7 +2428,7 @@
         <v>20</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="C6" s="24" t="s">
         <v>114</v>
@@ -2370,10 +2436,10 @@
     </row>
     <row r="7" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="24" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="C7" s="24" t="s">
         <v>117</v>
@@ -2381,18 +2447,18 @@
     </row>
     <row r="8" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="24" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="B8" s="27" t="s">
         <v>74</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="24" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="B9" s="27" t="s">
         <v>77</v>
@@ -2403,7 +2469,7 @@
     </row>
     <row r="10" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="24" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="B10" s="27" t="s">
         <v>79</v>
@@ -2417,18 +2483,18 @@
         <v>35</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="24" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="C12" s="24" t="s">
         <v>131</v>
@@ -2436,13 +2502,13 @@
     </row>
     <row r="13" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="24" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>87</v>
+        <v>202</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2450,7 +2516,7 @@
         <v>44</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>90</v>
+        <v>204</v>
       </c>
       <c r="C14" s="24" t="s">
         <v>136</v>
@@ -2458,13 +2524,13 @@
     </row>
     <row r="15" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="24" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2472,20 +2538,20 @@
         <v>49</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="D16" s="28"/>
     </row>
     <row r="17" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="29"/>
       <c r="B17" s="24" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="C17" s="30" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/setlists/Stove Up.xlsx
+++ b/setlists/Stove Up.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="202">
   <si>
     <t xml:space="preserve">SET 1</t>
   </si>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">Smithereens</t>
   </si>
   <si>
-    <t xml:space="preserve">All Right Now ↓</t>
+    <t xml:space="preserve">All Right Now</t>
   </si>
   <si>
     <t xml:space="preserve">Ivory</t>
@@ -112,7 +112,366 @@
     <t xml:space="preserve">Gin Blossoms</t>
   </si>
   <si>
-    <t xml:space="preserve">All For You ↓</t>
+    <t xml:space="preserve">Mr Jones &amp; Me</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V: Am F Dm G – Am F G, C: CFG
+B: Am F Am G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Counting Crowes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cover Me ↓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V: (Bm Em) - G A
+B: (Em Bm) F#</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bruce Springsteen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Long Way Down</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goo Goo Dolls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Counting Blue Cars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V:Bm A G  C: D E G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dishwalla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cocaine ↓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E Mix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eric Clapton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bad Case of Loving You ↓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robert Palmer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beast of Burden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E B C#m A – A E/G# A B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rolling Stones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What I Like About You</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E Mix, Harp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Romantics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SET 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nothing But A Good Time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V:A G D  C: G D A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Would?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F#m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice in Chains</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boys of Summer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Em/G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Don Henley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Alone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V: (G D C) B C: E B G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rockin' in the Free World</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V: Em D C
+C: G D C – Em - A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neil Young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hemorrhage in my Hands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ivory </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bm / A Mix
+I: Bm A G – Ends on A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drp Db</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stuck In The Middle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V: D G D – A C G – D
+B: G D – G D A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stealers Wheel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lump</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Presidents of the USA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collective Soul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Std</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* Ivory Filibuster *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tuning change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Working For the Weekend ↓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loverboy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summer of '69 ↓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V: D A – Bm A D G
+B: F Bb C Bb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bryan Adams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flagpole Sitta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V:D Am C D  B: A G F G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harvey Danger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She's A Beauty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K+I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Tubes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Own Worst Enemy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E F# A B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Don't You Forget About Me</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I: D E, D E C D,D E
+V: E D A D, B: C G D A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simple Minds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SET 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miss You</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Am Dm – F Em Dm – E#9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Was Made For Lovin You</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Em – Am, (Em G B [Em/A])</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hold the Line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crackerman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A B, E F#, B: F# A D E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power Of Love</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F / Cm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huey Lewis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aeroplane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gm – C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RHCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inside Out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C: A E F# - A E B -(E B F#)
+V: B F# A G B F# E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eve 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumbersome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F#</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seven Mary Three</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Movin' Out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dm – ends on D Major</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billy Joel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">American Band</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grand Funk Railroad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">December</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G F C Bb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santa Monica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Everclear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D C E G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cracker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mary Jane's Last Dance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V: Am G D Am  C: D A  G, Harp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Petty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Champagne Supernova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Harp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oasis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other / Ideas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All For You</t>
   </si>
   <si>
     <t xml:space="preserve">V: (Am D)(Em Am)
@@ -122,386 +481,6 @@
     <t xml:space="preserve">Sister Hazel</t>
   </si>
   <si>
-    <t xml:space="preserve">Mr Jones &amp; Me</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V: Am F Dm G – Am F G, C: CFG
-B: Am F Am G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Counting Crowes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cover Me ↓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V: (Bm Em) - G A
-B: (Em Bm) F#</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bruce Springsteen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Long Way Down</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bm </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Goo Goo Dolls</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Counting Blue Cars</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V:Bm A G  C: D E G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dishwalla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cocaine ↓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E Mix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eric Clapton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bad Case of Loving You ↓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robert Palmer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What I Like About You</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E Mix, Harp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Romantics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SET 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nothing But A Good Time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V:A G D  C: G D A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Poison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Would?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F#m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice in Chains</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boys of Summer ↓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Em/G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Don Henley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Alone ↓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V: (G D C) B C: E B G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Live</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rockin' in the Free World</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V: Em D C
-C: G D C – Em - A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neil Young</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hemorrhage in my Hands</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ivory </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bm / A Mix
-I: Bm A G – Ends on A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fuel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drp Db</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stuck In The Middle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V: D G D – A C G – D
-B: G D – G D A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stealers Wheel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lump</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Presidents of the USA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Collective Soul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Std</t>
-  </si>
-  <si>
-    <t xml:space="preserve">* Ivory Filibuster *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tuning change</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Working For the Weekend ↓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loverboy</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Summer of '69</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> ↓</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">V: D A – Bm A D G
-B: F Bb C Bb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bryan Adams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flagpole Sitta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V:D Am C D  B: A G F G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harvey Danger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">She's A Beauty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K+I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Tubes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My Own Worst Enemy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E F# A B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Don't You Forget About Me</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I: D E, D E C D,D E
-V: E D A D, B: C G D A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simple Minds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SET 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miss You ↓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Am Dm – F Em Dm – E#9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rolling Stones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Was Made For Lovin You</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Em – Am, (Em G B [Em/A])</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hold the Line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crackerman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A B, E F#, B: F# A D E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aeroplane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gm – C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RHCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inside Out ↓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C: A E F# - A E B -(E B F#)
-V: B F# A G B F# E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eve 6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cumbersome</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F#</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seven Mary Three</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beast of Burden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E B C#m A – A E/G# A B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Movin' Out ↓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dm – ends on D Major</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billy Joel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">American Band</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grand Funk Railroad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">December ↓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G F C Bb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santa Monica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Everclear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D C E G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cracker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mary Jane's Last Dance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V: Am G D Am  C: D A  G, Harp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Petty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Champagne Supernova</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Harp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oasis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other / Ideas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billie Jean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Em -Am, (Em C) B7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michael Jackson</t>
-  </si>
-  <si>
     <t xml:space="preserve">Blitzkreig Bop</t>
   </si>
   <si>
@@ -540,6 +519,9 @@
     <t xml:space="preserve">Better Than Ezra</t>
   </si>
   <si>
+    <t xml:space="preserve">?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Head Over Heels</t>
   </si>
   <si>
@@ -567,15 +549,6 @@
     <t xml:space="preserve">Black Sabbath</t>
   </si>
   <si>
-    <t xml:space="preserve">Power Of Love</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E / Bm </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Huey Lewis</t>
-  </si>
-  <si>
     <t xml:space="preserve">Run To You</t>
   </si>
   <si>
@@ -603,27 +576,18 @@
     <t xml:space="preserve">Set 3</t>
   </si>
   <si>
-    <t xml:space="preserve">Nothin’ But A Good ↓</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Would?</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - I Was Made 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - All Right Now ↓</t>
+    <t xml:space="preserve">Nothin’ But A Good</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Was Made For</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - All Right Now</t>
   </si>
   <si>
     <t xml:space="preserve">Hold The Line</t>
   </si>
   <si>
-    <t xml:space="preserve"> - Fire on Mountain</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - I Alone</t>
-  </si>
-  <si>
     <t xml:space="preserve">Rockin' in the Free</t>
   </si>
   <si>
@@ -636,58 +600,46 @@
     <t xml:space="preserve">Found Out About U ↓</t>
   </si>
   <si>
-    <t xml:space="preserve"> - Cumbersome</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - All For You ↓</t>
-  </si>
-  <si>
     <t xml:space="preserve"> - Mr Jones &amp; Me</t>
   </si>
   <si>
+    <t xml:space="preserve"> - Long Way Down</t>
+  </si>
+  <si>
     <t xml:space="preserve">* Filibuster *</t>
   </si>
   <si>
-    <t xml:space="preserve"> - American Band</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Long Way Down</t>
+    <t xml:space="preserve"> Counting Blue Cars</t>
   </si>
   <si>
     <t xml:space="preserve">Working For Week</t>
   </si>
   <si>
-    <t xml:space="preserve"> Counting Blue Cars</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summer of '69 ↓</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Santa Monica</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Flagpole Sitta</t>
+    <t xml:space="preserve">Summer of '69</t>
   </si>
   <si>
     <t xml:space="preserve"> - Bad Case of Loving</t>
   </si>
   <si>
+    <t xml:space="preserve">Beast Of Burden</t>
+  </si>
+  <si>
     <t xml:space="preserve">She’s A Beauty</t>
   </si>
   <si>
+    <t xml:space="preserve">My Own Worst En ↓</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mary Jane's Last</t>
   </si>
   <si>
-    <t xml:space="preserve">My Own Worst En ↓</t>
+    <t xml:space="preserve"> - Don't You Forget</t>
   </si>
   <si>
     <t xml:space="preserve">Champ Supernova</t>
   </si>
   <si>
-    <t xml:space="preserve"> - Don't You Forget</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blitz, Jealousy, Lovesong, Semi-Charm, Cinnamon</t>
+    <t xml:space="preserve">Blitz, Jealousy, Lovesong, Semi-Charm,All4U</t>
   </si>
 </sst>
 </file>
@@ -748,12 +700,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b val="true"/>
       <sz val="20"/>
       <color theme="1"/>
@@ -773,6 +719,12 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="16"/>
@@ -867,7 +819,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -956,35 +908,43 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1175,8 +1135,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F1048576"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="24.3" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F69"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="27.73"/>
@@ -1259,7 +1219,7 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10"/>
+      <c r="A5" s="0"/>
       <c r="B5" s="8" t="s">
         <v>16</v>
       </c>
@@ -1331,15 +1291,15 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13"/>
+      <c r="A9" s="10"/>
       <c r="B9" s="8" t="s">
         <v>29</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>30</v>
@@ -1349,15 +1309,15 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10"/>
+      <c r="A10" s="11"/>
       <c r="B10" s="8" t="s">
         <v>32</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>33</v>
@@ -1372,10 +1332,10 @@
         <v>35</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>121</v>
+        <v>168</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>36</v>
@@ -1385,15 +1345,15 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11"/>
+      <c r="A12" s="7"/>
       <c r="B12" s="8" t="s">
         <v>38</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>168</v>
+        <v>100</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>39</v>
@@ -1403,15 +1363,15 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7"/>
+      <c r="A13" s="10"/>
       <c r="B13" s="8" t="s">
         <v>41</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>42</v>
@@ -1426,33 +1386,33 @@
         <v>44</v>
       </c>
       <c r="C14" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>146</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7"/>
+      <c r="B15" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D14" s="8" t="n">
-        <v>105</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10"/>
-      <c r="B15" s="8" t="s">
+      <c r="D15" s="8" t="n">
+        <v>101</v>
+      </c>
+      <c r="E15" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" s="8" t="n">
-        <v>146</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="14" t="s">
         <v>48</v>
       </c>
     </row>
@@ -1531,7 +1491,7 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10"/>
+      <c r="A21" s="7"/>
       <c r="B21" s="16" t="s">
         <v>60</v>
       </c>
@@ -1549,7 +1509,7 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="10"/>
+      <c r="A22" s="7"/>
       <c r="B22" s="16" t="s">
         <v>63</v>
       </c>
@@ -1567,7 +1527,7 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10"/>
+      <c r="A23" s="7"/>
       <c r="B23" s="16" t="s">
         <v>66</v>
       </c>
@@ -1797,7 +1757,7 @@
       <c r="F36" s="14"/>
     </row>
     <row r="37" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="10"/>
+      <c r="A37" s="7"/>
       <c r="B37" s="8" t="s">
         <v>103</v>
       </c>
@@ -1811,13 +1771,13 @@
         <v>104</v>
       </c>
       <c r="F37" s="9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="7"/>
+      <c r="B38" s="8" t="s">
         <v>105</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="10"/>
-      <c r="B38" s="8" t="s">
-        <v>106</v>
       </c>
       <c r="C38" s="8" t="s">
         <v>13</v>
@@ -1826,16 +1786,16 @@
         <v>128</v>
       </c>
       <c r="E38" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="F38" s="9" t="s">
         <v>107</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="7"/>
       <c r="B39" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C39" s="8" t="s">
         <v>6</v>
@@ -1847,13 +1807,13 @@
         <v>58</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="7"/>
       <c r="B40" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C40" s="8" t="s">
         <v>6</v>
@@ -1862,86 +1822,84 @@
         <v>149</v>
       </c>
       <c r="E40" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="F40" s="9" t="s">
         <v>112</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="7"/>
       <c r="B41" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D41" s="8" t="n">
+      <c r="D41" s="8"/>
+      <c r="E41" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="7"/>
+      <c r="B42" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D42" s="8" t="n">
         <v>101</v>
       </c>
-      <c r="E41" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="10"/>
-      <c r="B42" s="8" t="s">
+      <c r="E42" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="F42" s="9" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="0"/>
+      <c r="B43" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C43" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D42" s="8" t="n">
+      <c r="D43" s="8" t="n">
         <v>176</v>
       </c>
-      <c r="E42" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="10"/>
-      <c r="B43" s="8" t="s">
+      <c r="E43" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="F43" s="9" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="0"/>
+      <c r="B44" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="C44" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D43" s="8" t="n">
+      <c r="D44" s="8" t="n">
         <v>81</v>
       </c>
-      <c r="E43" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="F43" s="9" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="7"/>
-      <c r="B44" s="8" t="s">
+      <c r="E44" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="C44" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D44" s="8" t="n">
-        <v>101</v>
-      </c>
-      <c r="E44" s="8" t="s">
+      <c r="F44" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="F44" s="14" t="s">
-        <v>105</v>
-      </c>
     </row>
     <row r="45" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="10"/>
+      <c r="A45" s="0"/>
       <c r="B45" s="8" t="s">
         <v>125</v>
       </c>
@@ -1959,7 +1917,7 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="10"/>
+      <c r="A46" s="0"/>
       <c r="B46" s="8" t="s">
         <v>128</v>
       </c>
@@ -1977,7 +1935,7 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="11"/>
+      <c r="A47" s="0"/>
       <c r="B47" s="8" t="s">
         <v>131</v>
       </c>
@@ -1995,7 +1953,7 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="11"/>
+      <c r="A48" s="0"/>
       <c r="B48" s="8" t="s">
         <v>133</v>
       </c>
@@ -2081,27 +2039,27 @@
       <c r="F53" s="9"/>
     </row>
     <row r="54" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="7" t="s">
+      <c r="A54" s="7"/>
+      <c r="B54" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="B54" s="8" t="s">
+      <c r="C54" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" s="8" t="n">
+        <v>138</v>
+      </c>
+      <c r="E54" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="C54" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8" t="s">
+      <c r="F54" s="9" t="s">
         <v>148</v>
-      </c>
-      <c r="F54" s="9" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="7"/>
       <c r="B55" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C55" s="8" t="s">
         <v>13</v>
@@ -2110,16 +2068,16 @@
         <v>177</v>
       </c>
       <c r="E55" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="F55" s="9" t="s">
         <v>151</v>
-      </c>
-      <c r="F55" s="9" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="7"/>
       <c r="B56" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C56" s="8"/>
       <c r="D56" s="8" t="n">
@@ -2135,7 +2093,7 @@
     <row r="57" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="7"/>
       <c r="B57" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C57" s="8" t="s">
         <v>13</v>
@@ -2144,23 +2102,23 @@
         <v>83</v>
       </c>
       <c r="E57" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="F57" s="9" t="s">
         <v>155</v>
-      </c>
-      <c r="F57" s="9" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="7"/>
       <c r="B58" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C58" s="8" t="s">
         <v>17</v>
       </c>
       <c r="D58" s="8"/>
       <c r="E58" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F58" s="9" t="s">
         <v>19</v>
@@ -2169,7 +2127,7 @@
     <row r="59" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="7"/>
       <c r="B59" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C59" s="8" t="s">
         <v>13</v>
@@ -2178,15 +2136,15 @@
         <v>110</v>
       </c>
       <c r="E59" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="F59" s="9" t="s">
         <v>160</v>
-      </c>
-      <c r="F59" s="9" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="7" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="B60" s="8" t="s">
         <v>162</v>
@@ -2253,25 +2211,17 @@
       </c>
     </row>
     <row r="64" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="7"/>
-      <c r="B64" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="C64" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="D64" s="8"/>
-      <c r="E64" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="F64" s="9" t="s">
-        <v>173</v>
-      </c>
+      <c r="A64" s="0"/>
+      <c r="B64" s="0"/>
+      <c r="C64" s="0"/>
+      <c r="D64" s="0"/>
+      <c r="E64" s="0"/>
+      <c r="F64" s="0"/>
     </row>
     <row r="65" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="7"/>
       <c r="B65" s="8" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C65" s="8" t="s">
         <v>6</v>
@@ -2287,7 +2237,7 @@
     <row r="66" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="7"/>
       <c r="B66" s="8" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C66" s="8" t="s">
         <v>6</v>
@@ -2296,7 +2246,7 @@
         <v>115</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F66" s="9" t="s">
         <v>72</v>
@@ -2305,7 +2255,7 @@
     <row r="67" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="7"/>
       <c r="B67" s="8" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C67" s="8" t="s">
         <v>6</v>
@@ -2314,10 +2264,10 @@
         <v>102</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F67" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2328,21 +2278,6 @@
       <c r="A69" s="2"/>
       <c r="F69" s="2"/>
     </row>
-    <row r="1048562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -2369,13 +2304,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="22" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D1" s="23"/>
     </row>
@@ -2384,7 +2319,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C2" s="24" t="s">
         <v>103</v>
@@ -2395,32 +2330,32 @@
         <v>9</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>184</v>
+        <v>57</v>
       </c>
       <c r="C3" s="26" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="24" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B4" s="25" t="s">
         <v>60</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="24" t="s">
-        <v>188</v>
+        <v>16</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>189</v>
+        <v>63</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2428,48 +2363,48 @@
         <v>20</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="24" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="24" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B8" s="27" t="s">
         <v>74</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>194</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="24" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="B9" s="27" t="s">
         <v>77</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>123</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="24" t="s">
-        <v>196</v>
+        <v>32</v>
       </c>
       <c r="B10" s="27" t="s">
         <v>79</v>
@@ -2480,21 +2415,21 @@
     </row>
     <row r="11" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="24" t="s">
-        <v>35</v>
+        <v>189</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>198</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="24" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="C12" s="24" t="s">
         <v>131</v>
@@ -2502,21 +2437,21 @@
     </row>
     <row r="13" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="24" t="s">
-        <v>201</v>
+        <v>41</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>203</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="24" t="s">
-        <v>44</v>
+        <v>194</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>204</v>
+        <v>90</v>
       </c>
       <c r="C14" s="24" t="s">
         <v>136</v>
@@ -2524,37 +2459,42 @@
     </row>
     <row r="15" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="24" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="C15" s="24" t="s">
-        <v>207</v>
+        <v>196</v>
+      </c>
+      <c r="C15" s="29" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="24" t="s">
+      <c r="A16" s="29" t="s">
         <v>49</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="D16" s="28"/>
     </row>
     <row r="17" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="29"/>
+      <c r="A17" s="30"/>
       <c r="B17" s="24" t="s">
-        <v>210</v>
-      </c>
-      <c r="C17" s="30" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+        <v>199</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="31"/>
+      <c r="C18" s="32" t="s">
+        <v>201</v>
+      </c>
+    </row>
     <row r="19" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="20" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>

--- a/setlists/Stove Up.xlsx
+++ b/setlists/Stove Up.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="203">
   <si>
     <t xml:space="preserve">SET 1</t>
   </si>
@@ -589,6 +589,9 @@
   </si>
   <si>
     <t xml:space="preserve">Rockin' in the Free</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Power of Love</t>
   </si>
   <si>
     <t xml:space="preserve"> - Backwater</t>
@@ -819,7 +822,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -928,6 +931,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -936,15 +943,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1219,7 +1218,7 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0"/>
+      <c r="A5" s="2"/>
       <c r="B5" s="8" t="s">
         <v>16</v>
       </c>
@@ -1863,7 +1862,7 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0"/>
+      <c r="A43" s="2"/>
       <c r="B43" s="8" t="s">
         <v>119</v>
       </c>
@@ -1881,7 +1880,7 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0"/>
+      <c r="A44" s="2"/>
       <c r="B44" s="8" t="s">
         <v>122</v>
       </c>
@@ -1899,7 +1898,7 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0"/>
+      <c r="A45" s="2"/>
       <c r="B45" s="8" t="s">
         <v>125</v>
       </c>
@@ -1917,7 +1916,7 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0"/>
+      <c r="A46" s="2"/>
       <c r="B46" s="8" t="s">
         <v>128</v>
       </c>
@@ -1935,7 +1934,7 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0"/>
+      <c r="A47" s="2"/>
       <c r="B47" s="8" t="s">
         <v>131</v>
       </c>
@@ -1953,7 +1952,7 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0"/>
+      <c r="A48" s="2"/>
       <c r="B48" s="8" t="s">
         <v>133</v>
       </c>
@@ -2211,12 +2210,8 @@
       </c>
     </row>
     <row r="64" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0"/>
-      <c r="B64" s="0"/>
-      <c r="C64" s="0"/>
-      <c r="D64" s="0"/>
-      <c r="E64" s="0"/>
-      <c r="F64" s="0"/>
+      <c r="A64" s="2"/>
+      <c r="F64" s="2"/>
     </row>
     <row r="65" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="7"/>
@@ -2365,48 +2360,48 @@
       <c r="B6" s="25" t="s">
         <v>184</v>
       </c>
-      <c r="C6" s="24" t="s">
-        <v>116</v>
+      <c r="C6" s="27" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="24" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="24" t="s">
-        <v>187</v>
-      </c>
-      <c r="B8" s="27" t="s">
+        <v>188</v>
+      </c>
+      <c r="B8" s="28" t="s">
         <v>74</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="B9" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="B9" s="28" t="s">
         <v>77</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>46</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="28" t="s">
         <v>79</v>
       </c>
       <c r="C10" s="24" t="s">
@@ -2415,10 +2410,10 @@
     </row>
     <row r="11" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="24" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C11" s="24" t="s">
         <v>128</v>
@@ -2426,10 +2421,10 @@
     </row>
     <row r="12" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="24" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C12" s="24" t="s">
         <v>131</v>
@@ -2440,7 +2435,7 @@
         <v>41</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C13" s="24" t="s">
         <v>133</v>
@@ -2448,9 +2443,9 @@
     </row>
     <row r="14" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="24" t="s">
-        <v>194</v>
-      </c>
-      <c r="B14" s="28" t="s">
+        <v>195</v>
+      </c>
+      <c r="B14" s="29" t="s">
         <v>90</v>
       </c>
       <c r="C14" s="24" t="s">
@@ -2459,10 +2454,10 @@
     </row>
     <row r="15" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="24" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C15" s="29" t="s">
         <v>152</v>
@@ -2473,29 +2468,30 @@
         <v>49</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>198</v>
-      </c>
-      <c r="D16" s="28"/>
+        <v>199</v>
+      </c>
+      <c r="D16" s="29"/>
     </row>
     <row r="17" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="30"/>
       <c r="B17" s="24" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="31"/>
-      <c r="C18" s="32" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="C18" s="31" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C19" s="0"/>
+    </row>
     <row r="20" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/setlists/Stove Up.xlsx
+++ b/setlists/Stove Up.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="199">
   <si>
     <t xml:space="preserve">SET 1</t>
   </si>
@@ -567,15 +567,6 @@
     <t xml:space="preserve">Third Eye Blind</t>
   </si>
   <si>
-    <t xml:space="preserve">Set 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set 3</t>
-  </si>
-  <si>
     <t xml:space="preserve">Nothin’ But A Good</t>
   </si>
   <si>
@@ -612,9 +603,6 @@
     <t xml:space="preserve">* Filibuster *</t>
   </si>
   <si>
-    <t xml:space="preserve"> Counting Blue Cars</t>
-  </si>
-  <si>
     <t xml:space="preserve">Working For Week</t>
   </si>
   <si>
@@ -630,19 +618,19 @@
     <t xml:space="preserve">She’s A Beauty</t>
   </si>
   <si>
+    <t xml:space="preserve">Mary Jane's Last</t>
+  </si>
+  <si>
     <t xml:space="preserve">My Own Worst En ↓</t>
   </si>
   <si>
-    <t xml:space="preserve">Mary Jane's Last</t>
+    <t xml:space="preserve">Champ Supernova</t>
   </si>
   <si>
     <t xml:space="preserve"> - Don't You Forget</t>
   </si>
   <si>
-    <t xml:space="preserve">Champ Supernova</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blitz, Jealousy, Lovesong, Semi-Charm,All4U</t>
+    <t xml:space="preserve">Blitz, Cinnamon, Jealousy, Lovesong, SemiCh, All4U</t>
   </si>
 </sst>
 </file>
@@ -652,7 +640,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="11">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -703,31 +691,11 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="20"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="20"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <sz val="16"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="16"/>
@@ -737,7 +705,7 @@
     </font>
     <font>
       <i val="true"/>
-      <sz val="12"/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -822,7 +790,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="29">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -911,7 +879,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -919,35 +903,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2289,7 +2245,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D1048576"/>
   <sheetFormatPr defaultColWidth="32.53515625" defaultRowHeight="34.35" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="30.97"/>
@@ -2299,200 +2255,183 @@
   <sheetData>
     <row r="1" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="23" t="s">
         <v>177</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="C1" s="22" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="24" t="s">
         <v>178</v>
       </c>
-      <c r="C1" s="22" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="22" t="s">
         <v>179</v>
       </c>
-      <c r="D1" s="23"/>
-    </row>
-    <row r="2" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="25" t="s">
+      <c r="B3" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" s="22" t="s">
         <v>180</v>
       </c>
-      <c r="C2" s="24" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>181</v>
-      </c>
     </row>
     <row r="4" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="24" t="s">
-        <v>182</v>
-      </c>
-      <c r="B4" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" s="24" t="s">
-        <v>183</v>
+      <c r="A4" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="25" t="s">
-        <v>63</v>
+        <v>20</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>181</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>110</v>
+        <v>182</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="25" t="s">
+      <c r="A6" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="B6" s="23" t="s">
         <v>184</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="C6" s="22" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="22" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="24" t="s">
+      <c r="B7" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="22" t="s">
         <v>186</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B8" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="C7" s="24" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="24" t="s">
+      <c r="B10" s="24" t="s">
         <v>188</v>
       </c>
-      <c r="B8" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="24" t="s">
+      <c r="C10" s="22" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="22" t="s">
         <v>189</v>
       </c>
-      <c r="B9" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="C9" s="24" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="24" t="s">
+      <c r="C11" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="22" t="s">
         <v>190</v>
       </c>
-      <c r="B11" s="26" t="s">
+      <c r="C12" s="22" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="22" t="s">
         <v>191</v>
       </c>
-      <c r="C11" s="24" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="24" t="s">
+      <c r="B13" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="22" t="s">
         <v>192</v>
       </c>
-      <c r="B12" s="24" t="s">
+      <c r="B14" s="22" t="s">
         <v>193</v>
       </c>
-      <c r="C12" s="24" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="24" t="s">
+      <c r="C14" s="22" t="s">
         <v>194</v>
       </c>
-      <c r="C13" s="24" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="24" t="s">
+    </row>
+    <row r="15" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="22" t="s">
         <v>195</v>
       </c>
-      <c r="B14" s="29" t="s">
-        <v>90</v>
-      </c>
-      <c r="C14" s="24" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="24" t="s">
+      <c r="C15" s="22" t="s">
         <v>196</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="D15" s="26"/>
+    </row>
+    <row r="16" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="27"/>
+      <c r="B16" s="22" t="s">
         <v>197</v>
       </c>
-      <c r="C15" s="29" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="29" t="s">
-        <v>49</v>
-      </c>
-      <c r="B16" s="24" t="s">
+      <c r="C16" s="28" t="s">
         <v>198</v>
       </c>
-      <c r="C16" s="24" t="s">
-        <v>199</v>
-      </c>
-      <c r="D16" s="29"/>
-    </row>
-    <row r="17" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="30"/>
-      <c r="B17" s="24" t="s">
-        <v>200</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C18" s="31" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C19" s="0"/>
-    </row>
-    <row r="20" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    </row>
+    <row r="17" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="18" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="19" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/setlists/Stove Up.xlsx
+++ b/setlists/Stove Up.xlsx
@@ -634,7 +634,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -676,13 +676,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="16"/>
@@ -772,7 +765,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -821,24 +814,8 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -849,31 +826,31 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -886,47 +863,6 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB2B2B2"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDDDDDD"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1313,7 +1249,7 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="7" t="s">
         <v>38</v>
       </c>
       <c r="B12" s="7" t="s">
@@ -1322,7 +1258,7 @@
       <c r="C12" s="7" t="n">
         <v>177</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="12" t="s">
         <v>39</v>
       </c>
       <c r="E12" s="7" t="s">
@@ -1599,7 +1535,7 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="12" t="s">
+      <c r="A28" s="7" t="s">
         <v>86</v>
       </c>
       <c r="B28" s="7" t="s">
@@ -1608,7 +1544,7 @@
       <c r="C28" s="7" t="n">
         <v>152</v>
       </c>
-      <c r="D28" s="14" t="s">
+      <c r="D28" s="13" t="s">
         <v>39</v>
       </c>
       <c r="E28" s="7" t="s">
@@ -1655,7 +1591,7 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="12" t="s">
+      <c r="A31" s="7" t="s">
         <v>94</v>
       </c>
       <c r="B31" s="7" t="s">
@@ -1664,7 +1600,7 @@
       <c r="C31" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="D31" s="13" t="s">
+      <c r="D31" s="12" t="s">
         <v>39</v>
       </c>
       <c r="E31" s="7" t="s">
@@ -1756,7 +1692,7 @@
       <c r="C36" s="7" t="n">
         <v>174</v>
       </c>
-      <c r="D36" s="15"/>
+      <c r="D36" s="12"/>
       <c r="E36" s="7" t="s">
         <v>110</v>
       </c>
@@ -1765,7 +1701,7 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="16" t="s">
+      <c r="A37" s="7" t="s">
         <v>112</v>
       </c>
       <c r="B37" s="7" t="s">
@@ -1774,7 +1710,7 @@
       <c r="C37" s="7" t="n">
         <v>142</v>
       </c>
-      <c r="D37" s="13" t="s">
+      <c r="D37" s="12" t="s">
         <v>113</v>
       </c>
       <c r="E37" s="7"/>
@@ -1873,7 +1809,7 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="12" t="s">
+      <c r="A43" s="7" t="s">
         <v>129</v>
       </c>
       <c r="B43" s="7" t="s">
@@ -1882,7 +1818,7 @@
       <c r="C43" s="7" t="n">
         <v>129</v>
       </c>
-      <c r="D43" s="17" t="s">
+      <c r="D43" s="13" t="s">
         <v>39</v>
       </c>
       <c r="E43" s="7" t="s">
@@ -1927,7 +1863,7 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="12" t="s">
+      <c r="A46" s="7" t="s">
         <v>138</v>
       </c>
       <c r="B46" s="7" t="s">
@@ -1936,7 +1872,7 @@
       <c r="C46" s="7" t="n">
         <v>132</v>
       </c>
-      <c r="D46" s="13" t="s">
+      <c r="D46" s="12" t="s">
         <v>39</v>
       </c>
       <c r="E46" s="7" t="s">
@@ -1981,7 +1917,7 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="18" t="s">
+      <c r="A49" s="14" t="s">
         <v>145</v>
       </c>
       <c r="B49" s="7" t="s">
@@ -2017,14 +1953,16 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="16" t="s">
+      <c r="A51" s="7" t="s">
         <v>151</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C51" s="7"/>
-      <c r="D51" s="13" t="s">
+      <c r="C51" s="7" t="n">
+        <v>140</v>
+      </c>
+      <c r="D51" s="12" t="s">
         <v>113</v>
       </c>
       <c r="E51" s="7" t="s">
@@ -2071,7 +2009,7 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="16" t="s">
+      <c r="A54" s="7" t="s">
         <v>158</v>
       </c>
       <c r="B54" s="7" t="s">
@@ -2080,7 +2018,7 @@
       <c r="C54" s="7" t="n">
         <v>75</v>
       </c>
-      <c r="D54" s="13" t="s">
+      <c r="D54" s="12" t="s">
         <v>113</v>
       </c>
       <c r="E54" s="7"/>
@@ -2089,7 +2027,7 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="16" t="s">
+      <c r="A55" s="7" t="s">
         <v>159</v>
       </c>
       <c r="B55" s="7" t="s">
@@ -2098,7 +2036,7 @@
       <c r="C55" s="7" t="n">
         <v>124</v>
       </c>
-      <c r="D55" s="15" t="s">
+      <c r="D55" s="12" t="s">
         <v>113</v>
       </c>
       <c r="E55" s="7" t="s">
@@ -2163,7 +2101,7 @@
       </c>
     </row>
     <row r="59" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="12" t="s">
+      <c r="A59" s="7" t="s">
         <v>170</v>
       </c>
       <c r="B59" s="7" t="s">
@@ -2172,7 +2110,7 @@
       <c r="C59" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="D59" s="13" t="s">
+      <c r="D59" s="12" t="s">
         <v>39</v>
       </c>
       <c r="E59" s="7" t="s">
@@ -2215,177 +2153,177 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="16" t="s">
         <v>172</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="15" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="17" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="15" t="s">
         <v>175</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="15" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="15" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="17" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="15" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="15" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="15" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="15" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="15" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="15" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="15" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="15" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="23" t="s">
+      <c r="A15" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="15" t="s">
         <v>194</v>
       </c>
-      <c r="D15" s="23"/>
+      <c r="D15" s="19"/>
     </row>
     <row r="16" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="24"/>
-      <c r="B16" s="19" t="s">
+      <c r="A16" s="20"/>
+      <c r="B16" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="C16" s="25" t="s">
+      <c r="C16" s="21" t="s">
         <v>196</v>
       </c>
     </row>

--- a/setlists/Stove Up.xlsx
+++ b/setlists/Stove Up.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="1" state="visible" r:id="rId3"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="196">
   <si>
     <t xml:space="preserve">Song</t>
   </si>
@@ -573,58 +573,55 @@
     <t xml:space="preserve">Rockin' in the Free</t>
   </si>
   <si>
+    <t xml:space="preserve"> - Backwater</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hemorrhage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Found Out About U ↓</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Mr Jones &amp; Me</t>
+  </si>
+  <si>
     <t xml:space="preserve">The Power of Love</t>
   </si>
   <si>
-    <t xml:space="preserve"> - Backwater</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hemorrhage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Found Out About U ↓</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Mr Jones &amp; Me</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cover Me ↓</t>
   </si>
   <si>
     <t xml:space="preserve"> - Long Way Down</t>
   </si>
   <si>
-    <t xml:space="preserve">* Filibuster *</t>
-  </si>
-  <si>
     <t xml:space="preserve">Working For Week</t>
   </si>
   <si>
     <t xml:space="preserve">Cocaine ↓</t>
   </si>
   <si>
+    <t xml:space="preserve">Mary Jane's Last</t>
+  </si>
+  <si>
     <t xml:space="preserve"> - Bad Case of Loving</t>
   </si>
   <si>
+    <t xml:space="preserve">She’s A Beauty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Champ Supernova</t>
+  </si>
+  <si>
     <t xml:space="preserve">Beast Of Burden</t>
   </si>
   <si>
-    <t xml:space="preserve">She’s A Beauty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mary Jane's Last</t>
-  </si>
-  <si>
     <t xml:space="preserve">My Own Worst En ↓</t>
   </si>
   <si>
-    <t xml:space="preserve">Champ Supernova</t>
+    <t xml:space="preserve">Blitz, Cinnamon, Jealousy, Lovesong, SemiCh, All4U</t>
   </si>
   <si>
     <t xml:space="preserve"> - Don't You Forget</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blitz, Cinnamon, Jealousy, Lovesong, SemiCh, All4U</t>
   </si>
 </sst>
 </file>
@@ -634,7 +631,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -685,12 +682,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="16"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <i val="true"/>
       <sz val="10"/>
       <name val="Arial"/>
@@ -708,19 +699,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFCC"/>
+        <bgColor rgb="FFEEEEEE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEEEEE"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDDDDD"/>
-        <bgColor rgb="FFCCFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2B2B2"/>
-        <bgColor rgb="FF969696"/>
+        <bgColor rgb="FFEEEEEE"/>
       </patternFill>
     </fill>
   </fills>
@@ -846,11 +837,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -879,11 +870,11 @@
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFB2B2B2"/>
+      <rgbColor rgb="FFC0C0C0"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFEEEEEE"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
@@ -2203,131 +2194,132 @@
       <c r="B5" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="C5" s="17" t="s">
-        <v>179</v>
+      <c r="C5" s="15" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="B6" s="16" t="s">
         <v>180</v>
       </c>
-      <c r="B6" s="16" t="s">
-        <v>181</v>
-      </c>
       <c r="C6" s="15" t="s">
-        <v>10</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B7" s="18" t="s">
         <v>159</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>100</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B8" s="18" t="s">
         <v>112</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>61</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="15" t="s">
-        <v>184</v>
+      <c r="A9" s="19" t="s">
+        <v>183</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>120</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>186</v>
+        <v>184</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>158</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>52</v>
+        <v>185</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>64</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>188</v>
+        <v>52</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>162</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>142</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B13" s="19" t="s">
         <v>75</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>109</v>
+        <v>188</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="B14" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="C14" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="C14" s="15" t="s">
+    </row>
+    <row r="15" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="15" t="s">
         <v>192</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="s">
-        <v>164</v>
       </c>
       <c r="B15" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="21" t="s">
         <v>194</v>
       </c>
       <c r="D15" s="19"/>
     </row>
     <row r="16" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="20"/>
+      <c r="A16" s="19" t="s">
+        <v>164</v>
+      </c>
       <c r="B16" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="C16" s="21" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    </row>
+    <row r="17" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="19"/>
+    </row>
     <row r="18" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="19" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/setlists/Stove Up.xlsx
+++ b/setlists/Stove Up.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="196">
   <si>
     <t xml:space="preserve">Song</t>
   </si>
@@ -600,28 +600,29 @@
     <t xml:space="preserve">Cocaine ↓</t>
   </si>
   <si>
+    <t xml:space="preserve"> - Bad Case of Loving</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She’s A Beauty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beast Of Burden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Own Worst En ↓</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mary Jane's Last</t>
   </si>
   <si>
-    <t xml:space="preserve"> - Bad Case of Loving</t>
-  </si>
-  <si>
-    <t xml:space="preserve">She’s A Beauty</t>
+    <t xml:space="preserve">X: All4U, Blitz, Jealousy
+Lovesong, SemiCh</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Don't You Forget</t>
   </si>
   <si>
     <t xml:space="preserve">Champ Supernova</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beast Of Burden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My Own Worst En ↓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blitz, Cinnamon, Jealousy, Lovesong, SemiCh, All4U</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Don't You Forget</t>
   </si>
 </sst>
 </file>
@@ -631,7 +632,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -680,6 +681,19 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i val="true"/>
@@ -756,7 +770,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -841,8 +855,24 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2282,45 +2312,51 @@
       <c r="B13" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="15" t="s">
-        <v>188</v>
+      <c r="C13" s="21" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="B14" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="C14" s="21" t="s">
         <v>190</v>
       </c>
-      <c r="C14" s="15" t="s">
+    </row>
+    <row r="15" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="B15" s="15" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="15" t="s">
+      <c r="C15" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="D15" s="19"/>
+    </row>
+    <row r="16" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="23" t="s">
         <v>193</v>
       </c>
-      <c r="C15" s="21" t="s">
+      <c r="B16" s="15" t="s">
         <v>194</v>
       </c>
-      <c r="D15" s="19"/>
-    </row>
-    <row r="16" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19" t="s">
-        <v>164</v>
-      </c>
-      <c r="B16" s="15" t="s">
+      <c r="C16" s="15" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="19"/>
-    </row>
-    <row r="18" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="C17" s="24"/>
+    </row>
+    <row r="18" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="25"/>
+    </row>
     <row r="19" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>

--- a/setlists/Stove Up.xlsx
+++ b/setlists/Stove Up.xlsx
@@ -694,6 +694,7 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <i val="true"/>
@@ -770,7 +771,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -843,6 +844,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -855,24 +860,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2244,7 +2237,7 @@
         <v>181</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>61</v>
@@ -2254,19 +2247,19 @@
       <c r="A8" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="B8" s="18" t="s">
-        <v>112</v>
+      <c r="B8" s="19" t="s">
+        <v>159</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="B9" s="18" t="s">
-        <v>151</v>
+      <c r="B9" s="19" t="s">
+        <v>112</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>20</v>
@@ -2276,7 +2269,7 @@
       <c r="A10" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="21" t="s">
         <v>158</v>
       </c>
       <c r="C10" s="15" t="s">
@@ -2309,10 +2302,10 @@
       <c r="A13" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="20" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2323,12 +2316,12 @@
       <c r="B14" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="20" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="15" t="s">
         <v>164</v>
       </c>
       <c r="B15" s="15" t="s">
@@ -2337,10 +2330,10 @@
       <c r="C15" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="D15" s="19"/>
+      <c r="D15" s="20"/>
     </row>
     <row r="16" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="22" t="s">
         <v>193</v>
       </c>
       <c r="B16" s="15" t="s">
@@ -2351,11 +2344,11 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="19"/>
-      <c r="C17" s="24"/>
+      <c r="B17" s="0"/>
+      <c r="C17" s="23"/>
     </row>
     <row r="18" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="25"/>
+      <c r="A18" s="20"/>
     </row>
     <row r="19" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/setlists/Stove Up.xlsx
+++ b/setlists/Stove Up.xlsx
@@ -5,11 +5,12 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Stove Up" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Stove Up 2 sets" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="200">
   <si>
     <t xml:space="preserve">Song</t>
   </si>
@@ -623,6 +624,18 @@
   </si>
   <si>
     <t xml:space="preserve">Champ Supernova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semi-Charmed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">--- Set 2 ---</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- All For You</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blitzkreig</t>
   </si>
 </sst>
 </file>
@@ -683,12 +696,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <i val="true"/>
       <sz val="10"/>
       <color theme="1"/>
@@ -699,6 +706,14 @@
     <font>
       <i val="true"/>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="16"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -771,7 +786,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -844,7 +859,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -860,12 +875,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2344,7 +2363,6 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="0"/>
       <c r="C17" s="23"/>
     </row>
     <row r="18" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2361,4 +2379,191 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="33.65" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="26.64"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="17" t="s">
+        <v>177</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="20"/>
+    </row>
+    <row r="15" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="15"/>
+    </row>
+    <row r="17" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="15"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/setlists/Stove Up.xlsx
+++ b/setlists/Stove Up.xlsx
@@ -632,7 +632,7 @@
     <t xml:space="preserve">--- Set 2 ---</t>
   </si>
   <si>
-    <t xml:space="preserve">- All For You</t>
+    <t xml:space="preserve"> - All For You</t>
   </si>
   <si>
     <t xml:space="preserve">Blitzkreig</t>
@@ -2389,7 +2389,7 @@
   <dimension ref="A1:C17"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="33.65" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26.4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="26.64"/>
   </cols>

--- a/setlists/Stove Up.xlsx
+++ b/setlists/Stove Up.xlsx
@@ -645,7 +645,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -711,6 +711,12 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="16"/>
       <color theme="1"/>
@@ -786,7 +792,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -883,7 +889,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2409,8 +2423,8 @@
       <c r="A2" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="B2" s="15" t="s">
-        <v>162</v>
+      <c r="B2" s="24" t="s">
+        <v>75</v>
       </c>
       <c r="C2" s="20" t="s">
         <v>159</v>
@@ -2420,8 +2434,8 @@
       <c r="A3" s="15" t="s">
         <v>175</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>75</v>
+      <c r="B3" s="25" t="s">
+        <v>162</v>
       </c>
       <c r="C3" s="20" t="s">
         <v>196</v>
@@ -2464,7 +2478,7 @@
       <c r="A7" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="26" t="s">
         <v>197</v>
       </c>
       <c r="C7" s="20" t="s">
@@ -2552,7 +2566,7 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="15"/>
+      <c r="B16" s="24"/>
     </row>
     <row r="17" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="15"/>

--- a/setlists/Stove Up.xlsx
+++ b/setlists/Stove Up.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="1" state="visible" r:id="rId3"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="207">
   <si>
     <t xml:space="preserve">Song</t>
   </si>
@@ -153,6 +153,18 @@
     <t xml:space="preserve">Don Henley</t>
   </si>
   <si>
+    <t xml:space="preserve">Burden In My Hand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eb ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B (down ½ step)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soundgarden</t>
+  </si>
+  <si>
     <t xml:space="preserve">Champagne Supernova</t>
   </si>
   <si>
@@ -418,6 +430,15 @@
   </si>
   <si>
     <t xml:space="preserve">Lit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No One Knows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cm G B – Cm Eb G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QOTSA</t>
   </si>
   <si>
     <t xml:space="preserve">Nothing But A Good Time</t>
@@ -645,7 +666,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -709,12 +730,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -792,7 +807,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -889,15 +904,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1084,7 +1091,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="27.73"/>
@@ -1320,152 +1327,154 @@
         <v>42</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>150</v>
-      </c>
-      <c r="D13" s="8"/>
+        <v>92</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>43</v>
+      </c>
       <c r="E13" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B14" s="7"/>
+        <v>46</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>7</v>
+      </c>
       <c r="C14" s="7" t="n">
-        <v>105</v>
+        <v>150</v>
       </c>
       <c r="D14" s="8"/>
       <c r="E14" s="7" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>7</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="B15" s="7"/>
       <c r="C15" s="7" t="n">
         <v>105</v>
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="7" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="D16" s="8"/>
       <c r="E16" s="7" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="D17" s="8"/>
       <c r="E17" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="D18" s="8"/>
       <c r="E18" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="D19" s="8"/>
       <c r="E19" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>81</v>
-      </c>
-      <c r="D20" s="10"/>
+        <v>149</v>
+      </c>
+      <c r="D20" s="8"/>
       <c r="E20" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>122</v>
+        <v>81</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="7" t="s">
@@ -1483,9 +1492,9 @@
         <v>69</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>111</v>
-      </c>
-      <c r="D22" s="8"/>
+        <v>122</v>
+      </c>
+      <c r="D22" s="10"/>
       <c r="E22" s="7" t="s">
         <v>70</v>
       </c>
@@ -1498,102 +1507,100 @@
         <v>72</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>77</v>
-      </c>
-      <c r="D23" s="10"/>
+        <v>111</v>
+      </c>
+      <c r="D23" s="8"/>
       <c r="E23" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>145</v>
-      </c>
-      <c r="D24" s="8"/>
+        <v>77</v>
+      </c>
+      <c r="D24" s="10"/>
       <c r="E24" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C26" s="7"/>
+        <v>7</v>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>135</v>
+      </c>
       <c r="D26" s="8"/>
       <c r="E26" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7" t="n">
-        <v>110</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="C27" s="7"/>
       <c r="D27" s="8"/>
       <c r="E27" s="7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>87</v>
+        <v>11</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>152</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>39</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="D28" s="8"/>
       <c r="E28" s="7" t="s">
         <v>88</v>
       </c>
@@ -1606,574 +1613,616 @@
         <v>90</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>7</v>
+        <v>91</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>153</v>
-      </c>
-      <c r="D29" s="8"/>
+        <v>152</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>39</v>
+      </c>
       <c r="E29" s="7" t="s">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>97</v>
+        <v>153</v>
       </c>
       <c r="D30" s="8"/>
       <c r="E30" s="7" t="s">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>90</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>39</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="D31" s="8"/>
       <c r="E31" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>128</v>
-      </c>
-      <c r="D32" s="8"/>
+        <v>90</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>39</v>
+      </c>
       <c r="E32" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>176</v>
-      </c>
-      <c r="D33" s="10"/>
+        <v>128</v>
+      </c>
+      <c r="D33" s="8"/>
       <c r="E33" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>168</v>
-      </c>
-      <c r="D34" s="8"/>
+        <v>176</v>
+      </c>
+      <c r="D34" s="10"/>
       <c r="E34" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>69</v>
+        <v>7</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>140</v>
+        <v>168</v>
       </c>
       <c r="D35" s="8"/>
       <c r="E35" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>174</v>
-      </c>
-      <c r="D36" s="12"/>
+        <v>140</v>
+      </c>
+      <c r="D36" s="8"/>
       <c r="E36" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>142</v>
-      </c>
-      <c r="D37" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="E37" s="7"/>
+        <v>174</v>
+      </c>
+      <c r="D37" s="12"/>
+      <c r="E37" s="7" t="s">
+        <v>114</v>
+      </c>
       <c r="F37" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>85</v>
-      </c>
-      <c r="D38" s="8"/>
-      <c r="E38" s="7" t="s">
-        <v>116</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="E38" s="7"/>
       <c r="F38" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="D39" s="8"/>
       <c r="E39" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>134</v>
-      </c>
-      <c r="D40" s="10"/>
+        <v>110</v>
+      </c>
+      <c r="D40" s="8"/>
       <c r="E40" s="7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>122</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>142</v>
-      </c>
-      <c r="D41" s="8"/>
+        <v>134</v>
+      </c>
+      <c r="D41" s="10"/>
       <c r="E41" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="D42" s="8"/>
       <c r="E42" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>129</v>
-      </c>
-      <c r="D43" s="13" t="s">
-        <v>39</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="D43" s="8"/>
       <c r="E43" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D44" s="8"/>
       <c r="E44" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C45" s="7"/>
-      <c r="D45" s="8"/>
+        <v>7</v>
+      </c>
+      <c r="C45" s="7" t="n">
+        <v>129</v>
+      </c>
+      <c r="D45" s="13" t="s">
+        <v>39</v>
+      </c>
       <c r="E45" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>132</v>
-      </c>
-      <c r="D46" s="12" t="s">
-        <v>39</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="D46" s="8"/>
       <c r="E46" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>46</v>
+        <v>141</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="7"/>
+        <v>11</v>
+      </c>
+      <c r="C47" s="7" t="n">
+        <v>120</v>
+      </c>
       <c r="D47" s="8"/>
       <c r="E47" s="7" t="s">
-        <v>92</v>
+        <v>143</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="D48" s="10"/>
+        <v>132</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>39</v>
+      </c>
       <c r="E48" s="7" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>144</v>
+        <v>50</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="14" t="s">
-        <v>145</v>
+      <c r="A49" s="7" t="s">
+        <v>147</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>91</v>
+        <v>127</v>
       </c>
       <c r="D49" s="8"/>
       <c r="E49" s="7" t="s">
-        <v>146</v>
+        <v>96</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C50" s="7" t="n">
-        <v>102</v>
-      </c>
-      <c r="D50" s="8"/>
+        <v>100</v>
+      </c>
+      <c r="D50" s="10"/>
       <c r="E50" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="7" t="s">
-        <v>151</v>
+      <c r="A51" s="14" t="s">
+        <v>152</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>140</v>
-      </c>
-      <c r="D51" s="12" t="s">
-        <v>113</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="D51" s="8"/>
       <c r="E51" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>65</v>
+        <v>7</v>
       </c>
       <c r="C52" s="7" t="n">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="D52" s="8"/>
       <c r="E52" s="7" t="s">
-        <v>8</v>
+        <v>156</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="7" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>115</v>
-      </c>
-      <c r="D53" s="8"/>
+        <v>140</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>117</v>
+      </c>
       <c r="E53" s="7" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>89</v>
+        <v>160</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="C54" s="7" t="n">
-        <v>75</v>
-      </c>
-      <c r="D54" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="E54" s="7"/>
+        <v>111</v>
+      </c>
+      <c r="D54" s="8"/>
+      <c r="E54" s="7" t="s">
+        <v>8</v>
+      </c>
       <c r="F54" s="9" t="s">
-        <v>67</v>
+        <v>162</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>69</v>
+        <v>7</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>124</v>
-      </c>
-      <c r="D55" s="12" t="s">
-        <v>113</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="D55" s="8"/>
       <c r="E55" s="7" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>161</v>
+        <v>93</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C56" s="7" t="n">
-        <v>139</v>
-      </c>
-      <c r="D56" s="8"/>
-      <c r="E56" s="7" t="s">
-        <v>163</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="E56" s="7"/>
       <c r="F56" s="9" t="s">
-        <v>141</v>
+        <v>71</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="7" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="C57" s="7" t="n">
-        <v>160</v>
-      </c>
-      <c r="D57" s="8"/>
+        <v>124</v>
+      </c>
+      <c r="D57" s="12" t="s">
+        <v>117</v>
+      </c>
       <c r="E57" s="7" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="7" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C58" s="7" t="n">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="D58" s="8"/>
       <c r="E58" s="7" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B59" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="7" t="n">
+        <v>160</v>
+      </c>
+      <c r="D59" s="8"/>
+      <c r="E59" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="7" t="n">
+        <v>147</v>
+      </c>
+      <c r="D60" s="8"/>
+      <c r="E60" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="B61" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C59" s="7" t="n">
+      <c r="C61" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="D59" s="12" t="s">
+      <c r="D61" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E59" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="F59" s="9" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D60" s="10"/>
-      <c r="F60" s="1"/>
-    </row>
-    <row r="61" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D61" s="10"/>
-      <c r="F61" s="1"/>
+      <c r="E61" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D62" s="10"/>
+      <c r="F62" s="1"/>
+    </row>
+    <row r="63" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D63" s="10"/>
+      <c r="F63" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2204,51 +2253,51 @@
         <v>35</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="B3" s="16" t="s">
         <v>38</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>10</v>
@@ -2256,43 +2305,43 @@
     </row>
     <row r="6" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="20" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>20</v>
@@ -2300,80 +2349,80 @@
     </row>
     <row r="10" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="D15" s="20"/>
     </row>
     <row r="16" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="22" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2413,7 +2462,7 @@
         <v>35</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="C1" s="20" t="s">
         <v>20</v>
@@ -2421,117 +2470,117 @@
     </row>
     <row r="2" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="B2" s="24" t="s">
-        <v>75</v>
+        <v>180</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>79</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="B3" s="25" t="s">
-        <v>162</v>
+        <v>182</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>169</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="B7" s="26" t="s">
-        <v>197</v>
+        <v>188</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>204</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="20" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>10</v>
@@ -2539,34 +2588,34 @@
     </row>
     <row r="13" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C14" s="20"/>
     </row>
     <row r="15" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="24"/>
+      <c r="B16" s="15"/>
     </row>
     <row r="17" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="15"/>

--- a/setlists/Stove Up.xlsx
+++ b/setlists/Stove Up.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="210">
   <si>
     <t xml:space="preserve">Song</t>
   </si>
@@ -466,6 +466,15 @@
   </si>
   <si>
     <t xml:space="preserve">Huey Lewis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pride</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B E A F#m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U2</t>
   </si>
   <si>
     <t xml:space="preserve">Rockin' in the Free World</t>
@@ -666,7 +675,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -708,6 +717,13 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="16"/>
@@ -807,7 +823,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -864,47 +880,51 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1091,7 +1111,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="27.73"/>
@@ -1364,7 +1384,9 @@
       <c r="A15" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B15" s="7"/>
+      <c r="B15" s="7" t="s">
+        <v>7</v>
+      </c>
       <c r="C15" s="7" t="n">
         <v>105</v>
       </c>
@@ -1961,68 +1983,70 @@
         <v>145</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>132</v>
-      </c>
-      <c r="D48" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D48" s="14" t="s">
         <v>39</v>
       </c>
       <c r="E48" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>50</v>
+        <v>147</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>127</v>
-      </c>
-      <c r="D49" s="8"/>
+        <v>132</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>39</v>
+      </c>
       <c r="E49" s="7" t="s">
-        <v>96</v>
+        <v>149</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>148</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C50" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="D50" s="10"/>
+        <v>127</v>
+      </c>
+      <c r="D50" s="8"/>
       <c r="E50" s="7" t="s">
-        <v>150</v>
+        <v>96</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="14" t="s">
+      <c r="A51" s="7" t="s">
         <v>152</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>91</v>
-      </c>
-      <c r="D51" s="8"/>
+        <v>100</v>
+      </c>
+      <c r="D51" s="10"/>
       <c r="E51" s="7" t="s">
         <v>153</v>
       </c>
@@ -2031,14 +2055,14 @@
       </c>
     </row>
     <row r="52" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="7" t="s">
+      <c r="A52" s="15" t="s">
         <v>155</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C52" s="7" t="n">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="D52" s="8"/>
       <c r="E52" s="7" t="s">
@@ -2056,11 +2080,9 @@
         <v>7</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>140</v>
-      </c>
-      <c r="D53" s="12" t="s">
-        <v>117</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="D53" s="8"/>
       <c r="E53" s="7" t="s">
         <v>159</v>
       </c>
@@ -2073,73 +2095,73 @@
         <v>161</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>69</v>
+        <v>7</v>
       </c>
       <c r="C54" s="7" t="n">
-        <v>111</v>
-      </c>
-      <c r="D54" s="8"/>
+        <v>140</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>117</v>
+      </c>
       <c r="E54" s="7" t="s">
-        <v>8</v>
+        <v>162</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D55" s="8"/>
       <c r="E55" s="7" t="s">
-        <v>164</v>
+        <v>8</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>93</v>
+        <v>165</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C56" s="7" t="n">
-        <v>75</v>
-      </c>
-      <c r="D56" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="E56" s="7"/>
+        <v>115</v>
+      </c>
+      <c r="D56" s="8"/>
+      <c r="E56" s="7" t="s">
+        <v>167</v>
+      </c>
       <c r="F56" s="9" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="7" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="C57" s="7" t="n">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="D57" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="E57" s="7" t="s">
-        <v>167</v>
-      </c>
+      <c r="E57" s="7"/>
       <c r="F57" s="9" t="s">
-        <v>168</v>
+        <v>71</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2147,35 +2169,37 @@
         <v>169</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="C58" s="7" t="n">
-        <v>139</v>
-      </c>
-      <c r="D58" s="8"/>
+        <v>124</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>117</v>
+      </c>
       <c r="E58" s="7" t="s">
         <v>170</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C59" s="7" t="n">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="D59" s="8"/>
       <c r="E59" s="7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2186,7 +2210,7 @@
         <v>7</v>
       </c>
       <c r="C60" s="7" t="n">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="D60" s="8"/>
       <c r="E60" s="7" t="s">
@@ -2201,28 +2225,46 @@
         <v>177</v>
       </c>
       <c r="B61" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="7" t="n">
+        <v>147</v>
+      </c>
+      <c r="D61" s="8"/>
+      <c r="E61" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="B62" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C61" s="7" t="n">
+      <c r="C62" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="D61" s="12" t="s">
+      <c r="D62" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E61" s="7" t="s">
+      <c r="E62" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="F61" s="9" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D62" s="10"/>
-      <c r="F62" s="1"/>
+      <c r="F62" s="9" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D63" s="10"/>
       <c r="F63" s="1"/>
+    </row>
+    <row r="64" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D64" s="10"/>
+      <c r="F64" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2249,187 +2291,187 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="C1" s="15" t="s">
+      <c r="B1" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="C1" s="16" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="B2" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="B2" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>181</v>
+      <c r="C2" s="18" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="B3" s="16" t="s">
+      <c r="A3" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B3" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="15" t="s">
-        <v>183</v>
+      <c r="C3" s="16" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="16" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="17" t="s">
-        <v>184</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="C5" s="15" t="s">
+      <c r="A5" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="C5" s="16" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="C6" s="15" t="s">
+      <c r="A6" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="C6" s="16" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="15" t="s">
-        <v>188</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="C7" s="15" t="s">
+      <c r="A7" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="C7" s="16" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15" t="s">
-        <v>189</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C8" s="15" t="s">
+      <c r="A8" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="C8" s="16" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="B9" s="19" t="s">
+      <c r="A9" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="B9" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="16" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="15" t="s">
-        <v>191</v>
-      </c>
-      <c r="B10" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="C10" s="15" t="s">
+      <c r="A10" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>168</v>
+      </c>
+      <c r="C10" s="16" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="15" t="s">
-        <v>192</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>193</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>149</v>
+      <c r="A11" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="B12" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="C12" s="15" t="s">
+      <c r="B12" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="C12" s="16" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="15" t="s">
-        <v>194</v>
-      </c>
-      <c r="B13" s="20" t="s">
+      <c r="A13" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="B13" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="21" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>196</v>
-      </c>
-      <c r="C14" s="20" t="s">
-        <v>197</v>
+      <c r="A14" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>198</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="D15" s="20"/>
+      <c r="A15" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="D15" s="21"/>
     </row>
     <row r="16" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="22" t="s">
-        <v>200</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>201</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>202</v>
+      <c r="A16" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C17" s="23"/>
+      <c r="C17" s="24"/>
     </row>
     <row r="18" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="20"/>
+      <c r="A18" s="21"/>
     </row>
     <row r="19" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -2458,167 +2500,167 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="15" t="s">
-        <v>193</v>
-      </c>
-      <c r="C1" s="20" t="s">
+      <c r="B1" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1" s="21" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="B2" s="15" t="s">
+      <c r="A2" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="B2" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="C2" s="20" t="s">
-        <v>166</v>
+      <c r="C2" s="21" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>169</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>203</v>
+      <c r="A3" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="B4" s="15" t="s">
-        <v>196</v>
-      </c>
-      <c r="C4" s="20" t="s">
+      <c r="B4" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="C4" s="21" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="17" t="s">
-        <v>184</v>
-      </c>
-      <c r="B5" s="15" t="s">
+      <c r="A5" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>207</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="C5" s="15" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>201</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="15" t="s">
-        <v>188</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>204</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="20" t="s">
-        <v>205</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="15" t="s">
-        <v>189</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>206</v>
-      </c>
-      <c r="C9" s="20" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="15" t="s">
-        <v>191</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="15" t="s">
-        <v>192</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="15" t="s">
-        <v>194</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="C14" s="20"/>
+      <c r="C14" s="21"/>
     </row>
     <row r="15" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="B15" s="15" t="s">
+      <c r="A15" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="B15" s="16" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="15"/>
+      <c r="B16" s="16"/>
     </row>
     <row r="17" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="15"/>
+      <c r="B17" s="16"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/setlists/Stove Up.xlsx
+++ b/setlists/Stove Up.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="213">
   <si>
     <t xml:space="preserve">Song</t>
   </si>
@@ -156,10 +156,7 @@
     <t xml:space="preserve">Burden In My Hand</t>
   </si>
   <si>
-    <t xml:space="preserve">Eb ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B (down ½ step)</t>
+    <t xml:space="preserve">B (down a step)</t>
   </si>
   <si>
     <t xml:space="preserve">Soundgarden</t>
@@ -300,6 +297,12 @@
     <t xml:space="preserve">Better Than Ezra</t>
   </si>
   <si>
+    <t xml:space="preserve">Green River</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCR</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hemorrhage in my Hands</t>
   </si>
   <si>
@@ -557,6 +560,12 @@
   <si>
     <t xml:space="preserve">V: D A – Bm A D G
 B: F Bb C Bb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Superstition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stevie Wonder</t>
   </si>
   <si>
     <t xml:space="preserve">What I Like About You</t>
@@ -721,9 +730,9 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="16"/>
@@ -880,12 +889,12 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1111,7 +1120,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="27.73"/>
@@ -1353,18 +1362,18 @@
         <v>92</v>
       </c>
       <c r="D13" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="F13" s="9" t="s">
         <v>44</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>7</v>
@@ -1374,15 +1383,15 @@
       </c>
       <c r="D14" s="8"/>
       <c r="E14" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F14" s="9" t="s">
         <v>47</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>7</v>
@@ -1395,12 +1404,12 @@
         <v>21</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>7</v>
@@ -1413,12 +1422,12 @@
         <v>27</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>11</v>
@@ -1428,15 +1437,15 @@
       </c>
       <c r="D17" s="8"/>
       <c r="E17" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" s="9" t="s">
         <v>54</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>11</v>
@@ -1446,15 +1455,15 @@
       </c>
       <c r="D18" s="8"/>
       <c r="E18" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F18" s="9" t="s">
         <v>57</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>11</v>
@@ -1464,15 +1473,15 @@
       </c>
       <c r="D19" s="8"/>
       <c r="E19" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F19" s="9" t="s">
         <v>60</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>7</v>
@@ -1482,15 +1491,15 @@
       </c>
       <c r="D20" s="8"/>
       <c r="E20" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F20" s="9" t="s">
         <v>63</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>11</v>
@@ -1500,69 +1509,69 @@
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="F21" s="9" t="s">
         <v>66</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" s="7" t="s">
         <v>68</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>69</v>
       </c>
       <c r="C22" s="7" t="n">
         <v>122</v>
       </c>
       <c r="D22" s="10"/>
       <c r="E22" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="F22" s="9" t="s">
         <v>70</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B23" s="7" t="s">
         <v>72</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>73</v>
       </c>
       <c r="C23" s="7" t="n">
         <v>111</v>
       </c>
       <c r="D23" s="8"/>
       <c r="E23" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F23" s="9" t="s">
         <v>74</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C24" s="7" t="n">
         <v>77</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="F24" s="9" t="s">
         <v>77</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>11</v>
@@ -1572,15 +1581,15 @@
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F25" s="9" t="s">
         <v>80</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>7</v>
@@ -1590,31 +1599,31 @@
       </c>
       <c r="D26" s="8"/>
       <c r="E26" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="F26" s="9" t="s">
         <v>83</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C27" s="7"/>
       <c r="D27" s="8"/>
       <c r="E27" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>11</v>
@@ -1624,48 +1633,42 @@
       </c>
       <c r="D28" s="8"/>
       <c r="E28" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F28" s="9" t="s">
         <v>88</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="9" t="s">
         <v>90</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C29" s="7" t="n">
-        <v>152</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>152</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F30" s="9" t="s">
         <v>94</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="7" t="n">
-        <v>153</v>
-      </c>
-      <c r="D30" s="8"/>
-      <c r="E30" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1676,492 +1679,492 @@
         <v>7</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>97</v>
+        <v>153</v>
       </c>
       <c r="D31" s="8"/>
       <c r="E31" s="7" t="s">
-        <v>96</v>
+        <v>21</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="7" t="n">
+        <v>97</v>
+      </c>
+      <c r="D32" s="8"/>
+      <c r="E32" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="F32" s="9" t="s">
         <v>98</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="7" t="n">
-        <v>90</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>128</v>
-      </c>
-      <c r="D33" s="8"/>
+        <v>90</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>39</v>
+      </c>
       <c r="E33" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="7" t="n">
+        <v>128</v>
+      </c>
+      <c r="D34" s="8"/>
+      <c r="E34" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="F34" s="9" t="s">
         <v>104</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="7" t="n">
-        <v>176</v>
-      </c>
-      <c r="D34" s="10"/>
-      <c r="E34" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>168</v>
-      </c>
-      <c r="D35" s="8"/>
+        <v>176</v>
+      </c>
+      <c r="D35" s="10"/>
       <c r="E35" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>140</v>
+        <v>168</v>
       </c>
       <c r="D36" s="8"/>
       <c r="E36" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C37" s="7" t="n">
+        <v>140</v>
+      </c>
+      <c r="D37" s="8"/>
+      <c r="E37" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="F37" s="9" t="s">
         <v>113</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C37" s="7" t="n">
-        <v>174</v>
-      </c>
-      <c r="D37" s="12"/>
-      <c r="E37" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>174</v>
+      </c>
+      <c r="D38" s="12"/>
+      <c r="E38" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="F38" s="9" t="s">
         <v>116</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C38" s="7" t="n">
-        <v>142</v>
-      </c>
-      <c r="D38" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="E38" s="7"/>
-      <c r="F38" s="9" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C39" s="7" t="n">
+        <v>142</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="E39" s="7"/>
+      <c r="F39" s="9" t="s">
         <v>119</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="7" t="n">
-        <v>85</v>
-      </c>
-      <c r="D39" s="8"/>
-      <c r="E39" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="D40" s="8"/>
       <c r="E40" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>31</v>
+        <v>122</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="7" t="n">
+        <v>110</v>
+      </c>
+      <c r="D41" s="8"/>
+      <c r="E41" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="B41" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C41" s="7" t="n">
-        <v>134</v>
-      </c>
-      <c r="D41" s="10"/>
-      <c r="E41" s="7" t="s">
-        <v>125</v>
-      </c>
       <c r="F41" s="9" t="s">
-        <v>126</v>
+        <v>31</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C42" s="7" t="n">
+        <v>134</v>
+      </c>
+      <c r="D42" s="10"/>
+      <c r="E42" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="F42" s="9" t="s">
         <v>127</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="7" t="n">
-        <v>142</v>
-      </c>
-      <c r="D42" s="8"/>
-      <c r="E42" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="D43" s="8"/>
       <c r="E43" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>170</v>
+        <v>103</v>
       </c>
       <c r="D44" s="8"/>
       <c r="E44" s="7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C45" s="7" t="n">
+        <v>170</v>
+      </c>
+      <c r="D45" s="8"/>
+      <c r="E45" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="F45" s="9" t="s">
         <v>136</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="7" t="n">
-        <v>129</v>
-      </c>
-      <c r="D45" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>163</v>
-      </c>
-      <c r="D46" s="8"/>
+        <v>129</v>
+      </c>
+      <c r="D46" s="13" t="s">
+        <v>39</v>
+      </c>
       <c r="E46" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>120</v>
+        <v>163</v>
       </c>
       <c r="D47" s="8"/>
       <c r="E47" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C48" s="7" t="n">
+        <v>120</v>
+      </c>
+      <c r="D48" s="8"/>
+      <c r="E48" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="F48" s="9" t="s">
         <v>145</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" s="7" t="n">
-        <v>106</v>
-      </c>
-      <c r="D48" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="F48" s="9" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="D49" s="12" t="s">
         <v>39</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>50</v>
+        <v>148</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C50" s="7" t="n">
+        <v>132</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E50" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="B50" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="7" t="n">
-        <v>127</v>
-      </c>
-      <c r="D50" s="8"/>
-      <c r="E50" s="7" t="s">
-        <v>96</v>
-      </c>
       <c r="F50" s="9" t="s">
-        <v>151</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="7" t="n">
+        <v>127</v>
+      </c>
+      <c r="D51" s="8"/>
+      <c r="E51" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="F51" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="B51" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C51" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="D51" s="10"/>
-      <c r="E51" s="7" t="s">
+    </row>
+    <row r="52" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="7" t="s">
         <v>153</v>
-      </c>
-      <c r="F51" s="9" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="15" t="s">
-        <v>155</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C52" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="D52" s="10"/>
+      <c r="E52" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C53" s="7" t="n">
         <v>91</v>
-      </c>
-      <c r="D52" s="8"/>
-      <c r="E52" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="F52" s="9" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="7" t="n">
-        <v>102</v>
       </c>
       <c r="D53" s="8"/>
       <c r="E53" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C54" s="7" t="n">
-        <v>140</v>
-      </c>
-      <c r="D54" s="12" t="s">
-        <v>117</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="D54" s="8"/>
       <c r="E54" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="7" t="n">
+        <v>140</v>
+      </c>
+      <c r="D55" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="F55" s="9" t="s">
         <v>164</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C55" s="7" t="n">
-        <v>111</v>
-      </c>
-      <c r="D55" s="8"/>
-      <c r="E55" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F55" s="9" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>7</v>
+        <v>68</v>
       </c>
       <c r="C56" s="7" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D56" s="8"/>
       <c r="E56" s="7" t="s">
-        <v>167</v>
+        <v>8</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>93</v>
+        <v>166</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="7" t="n">
+        <v>115</v>
+      </c>
+      <c r="D57" s="8"/>
+      <c r="E57" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="B57" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C57" s="7" t="n">
-        <v>75</v>
-      </c>
-      <c r="D57" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="E57" s="7"/>
       <c r="F57" s="9" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2169,102 +2172,134 @@
         <v>169</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="C58" s="7" t="n">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>170</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="E58" s="7"/>
       <c r="F58" s="9" t="s">
-        <v>171</v>
+        <v>70</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C59" s="7" t="n">
+        <v>124</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="F59" s="9" t="s">
         <v>172</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C59" s="7" t="n">
-        <v>139</v>
-      </c>
-      <c r="D59" s="8"/>
-      <c r="E59" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="F59" s="9" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C60" s="7" t="n">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="D60" s="8"/>
       <c r="E60" s="7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C61" s="7" t="n">
-        <v>147</v>
-      </c>
-      <c r="D61" s="8"/>
-      <c r="E61" s="7" t="s">
-        <v>178</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="B61" s="7"/>
+      <c r="C61" s="7"/>
+      <c r="D61" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="E61" s="7"/>
       <c r="F61" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="7" t="n">
+        <v>160</v>
+      </c>
+      <c r="D62" s="8"/>
+      <c r="E62" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="F62" s="9" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="B62" s="7" t="s">
+      <c r="B63" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="7" t="n">
+        <v>147</v>
+      </c>
+      <c r="D63" s="8"/>
+      <c r="E63" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="B64" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C62" s="7" t="n">
+      <c r="C64" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="D62" s="12" t="s">
+      <c r="D64" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E62" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="F62" s="9" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D63" s="10"/>
-      <c r="F63" s="1"/>
-    </row>
-    <row r="64" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D64" s="10"/>
-      <c r="F64" s="1"/>
+      <c r="E64" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="F64" s="9" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D65" s="10"/>
+      <c r="F65" s="1"/>
+    </row>
+    <row r="66" customFormat="false" ht="24.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D66" s="10"/>
+      <c r="F66" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2295,51 +2330,51 @@
         <v>35</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="B2" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="B2" s="17" t="s">
-        <v>180</v>
-      </c>
       <c r="C2" s="18" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B3" s="17" t="s">
         <v>38</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C5" s="16" t="s">
         <v>10</v>
@@ -2347,43 +2382,43 @@
     </row>
     <row r="6" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C9" s="16" t="s">
         <v>20</v>
@@ -2391,80 +2426,80 @@
     </row>
     <row r="10" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D15" s="21"/>
     </row>
     <row r="16" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="23" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2504,7 +2539,7 @@
         <v>35</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C1" s="21" t="s">
         <v>20</v>
@@ -2512,117 +2547,117 @@
     </row>
     <row r="2" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B12" s="16" t="s">
         <v>10</v>
@@ -2630,30 +2665,30 @@
     </row>
     <row r="13" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C14" s="21"/>
     </row>
     <row r="15" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="33.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
